--- a/content/post/drafts/weekly-picks/2025Ruka/men-points.xlsx
+++ b/content/post/drafts/weekly-picks/2025Ruka/men-points.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="522">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -119,6 +119,24 @@
     <t xml:space="preserve">136.931750656113</t>
   </si>
   <si>
+    <t xml:space="preserve">Federico Pellegrino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2808081955677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8872133380297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0858499819185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.253871515516</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pål Golberg</t>
   </si>
   <si>
@@ -143,6 +161,96 @@
     <t xml:space="preserve">122.677353184158</t>
   </si>
   <si>
+    <t xml:space="preserve">Antoine Cyr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0360522090395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1999909704399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7249103767858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.960953556265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Ogden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2600724156314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.9509528319145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44971121846829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.660736466014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friedrich Moch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9930008669976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81518586850096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8713570839061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.679543819405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mika Vermeulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0592431478938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66960430357104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9446284316745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.673475883139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Lapalus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2868956787035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83557776217343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1097520898675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.232225530744</t>
+  </si>
+  <si>
     <t xml:space="preserve">Emil Iversen</t>
   </si>
   <si>
@@ -158,6 +266,39 @@
     <t xml:space="preserve">100.416281214048</t>
   </si>
   <si>
+    <t xml:space="preserve">Gus Schumacher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7233614292176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8103300280189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5699391939964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1036306512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">William Poromaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7352091122971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3510715994482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6146172157061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7008979274514</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lauri Vuorinen</t>
   </si>
   <si>
@@ -173,18 +314,177 @@
     <t xml:space="preserve">92.4362556034135</t>
   </si>
   <si>
+    <t xml:space="preserve">Calle Halfvarsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0581301340895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0506744288832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.779670970042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.8884755330148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Thomas Jenssen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5332077452863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.673120884296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2063286295823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules Lapierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8834788909157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96542420645009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.32834330695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1772464043158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francesco De Fabiani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0758223592259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9360703549231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0118474083101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.0237401224591</t>
+  </si>
+  <si>
     <t xml:space="preserve">Even Northug</t>
   </si>
   <si>
     <t xml:space="preserve">67.7733125189832</t>
   </si>
   <si>
+    <t xml:space="preserve">Jens Burman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.919675156865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90636108232244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0317635069991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8577997461865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richard Jouve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3085398187634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.3530932682408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5339551074586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1955881944628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johan Häggström</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.230386062366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6234960248556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8538820872216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theo Schely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4303750388358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8371136885451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83027789043517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.097766617816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zanden McMullen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9474410946987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7376942661655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.78442723455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4695625954142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valerio Grond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7447917881014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60908168097862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.35387346908</t>
+  </si>
+  <si>
     <t xml:space="preserve">Håvard Solås Taugbøl</t>
   </si>
   <si>
     <t xml:space="preserve">55.4285711808128</t>
   </si>
   <si>
+    <t xml:space="preserve">Jules Chappaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.627431124463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44407664492036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3661182789358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4376260483192</t>
+  </si>
+  <si>
     <t xml:space="preserve">Joni Mäki</t>
   </si>
   <si>
@@ -197,12 +497,6 @@
     <t xml:space="preserve">53.7903762040233</t>
   </si>
   <si>
-    <t xml:space="preserve">Jan Thomas Jenssen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.673120884296</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ristomatti Hakola</t>
   </si>
   <si>
@@ -227,10 +521,25 @@
     <t xml:space="preserve">43.9219175109499</t>
   </si>
   <si>
+    <t xml:space="preserve">Beda Klee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0087660412692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.05131574408386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76347216839213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8235539537452</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sivert Wiig</t>
   </si>
   <si>
-    <t xml:space="preserve">41.288111927147</t>
+    <t xml:space="preserve">40.569247296968</t>
   </si>
   <si>
     <t xml:space="preserve">Remi Lindholm</t>
@@ -245,16 +554,46 @@
     <t xml:space="preserve">40.2327539025056</t>
   </si>
   <si>
+    <t xml:space="preserve">Marcus Grate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.6046366908264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.85101791438463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7536187764418</t>
+  </si>
+  <si>
     <t xml:space="preserve">Arsi Ruuskanen</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8591382950463</t>
+    <t xml:space="preserve">20.6057032011029</t>
   </si>
   <si>
     <t xml:space="preserve">17.6378162015318</t>
   </si>
   <si>
-    <t xml:space="preserve">39.4969544965781</t>
+    <t xml:space="preserve">38.2435194026346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Hjalmar Westgård</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0267671119508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2866578416071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3031166205495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6165415741074</t>
   </si>
   <si>
     <t xml:space="preserve">Emil Liekari</t>
@@ -290,6 +629,48 @@
     <t xml:space="preserve">33.4595909446622</t>
   </si>
   <si>
+    <t xml:space="preserve">Oskar Svensson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.4233173789274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.796277264146794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6270401147806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondrej Cerny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0234744538969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.27131161382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7521628400737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elia Barp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9164653781413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3318269736354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30576208283771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5540544346144</t>
+  </si>
+  <si>
     <t xml:space="preserve">Markus Vuorela</t>
   </si>
   <si>
@@ -302,52 +683,475 @@
     <t xml:space="preserve">29.9948087372297</t>
   </si>
   <si>
+    <t xml:space="preserve">Irineu Esteve Altimiras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andorra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83881605924832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.547807419174175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3335483142343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7201717926568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davide Graz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18873996743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19339046337438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3290024732266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7111329040389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Albert Kuchler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7315264013895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17761636440912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15767748609493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0668202518935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Stoelben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2892501176532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28404786365813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5732979813114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyril Fähndrich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2438721074186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18872682373997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04164317861658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4742421097751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Florian Notz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.726232422949847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.392450255265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1186826782149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ludek Seller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9901487079373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.210673794283306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2008225022206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anian Sossau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9411888048333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21021618139246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1514049862257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simone Dapra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2959375901972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90910608212722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77471660591621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9797602782406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remi Bourdin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9945602001411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89309418761832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75182456018424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6394789479436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janosch Brugger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.196468825082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81279430496052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11774855596486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1270116860074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edvin Anger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63852059707695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0871191945371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07405838288122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7996981744952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Hellweger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4602968810421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76452177033537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2248186513774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janik Riebli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1782554214822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96100306461842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1392584861006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paolo Ventura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0364501982573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.075166733278382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94108997485981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0527069063955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Niko Anttola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03477562530596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68233861733123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7171142426372</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lauri Mannila</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21354133009841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8811804294646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.094721759563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Niko Anttola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2882107192494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34326701449752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6314777337469</t>
+    <t xml:space="preserve">0.0417264664376678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1623157992856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2040422657233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier McKeever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98652929361133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30313483402279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599609933115996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8892740607501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter Wonders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69584305150782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90225465333071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75557612139249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.353673826231</t>
   </si>
   <si>
     <t xml:space="preserve">Wiljam Mattila</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8151568306824</t>
+    <t xml:space="preserve">15.0962922005034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zak Ketterson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31153480451816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36053048562298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31345256601208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9855178561532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivier Leveille</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93900500726964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88047004834322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85569582890601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6751708845189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Danielsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.842309343126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.42609894337061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4162103997554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Bögl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00783485710589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52514342465781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35057459055772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8835528723214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truls Gisselman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7489442356172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59423786195063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14402102068428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4872031182521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miha Simenc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06462391322654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02590833096302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.412736533098074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6777957110915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan-Friedrich Doerks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22890739757373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1746309074841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966284623020501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3698229280783</t>
   </si>
   <si>
     <t xml:space="preserve">Andreas Fjorden Ree</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14701392237818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86191198557607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0089259079542</t>
+    <t xml:space="preserve">10.1979073840123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92659577018902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Davies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Great Britain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.734936766045822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14550663472483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12614022329822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53671009197723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnny Hagenbuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.326951575906619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161971926921955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69645538965557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53147574067091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Fellner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52492987561916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14914235386252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.636790238963534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31086246844521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvar Johannes Alev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.132098055202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.836845989550548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20198326607999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49723533173144</t>
   </si>
   <si>
     <t xml:space="preserve">Eero Rantala</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68632284845668</t>
+    <t xml:space="preserve">6.11588473260095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin Himma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.497537686362957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2950994223858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.447298978510162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35026275751268</t>
   </si>
   <si>
     <t xml:space="preserve">Miro Karppanen</t>
@@ -356,154 +1160,424 @@
     <t xml:space="preserve">5.30513050761533</t>
   </si>
   <si>
+    <t xml:space="preserve">Måns Skoglund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19804006775015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.091226419935203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10681364781495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathis Desloges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22194039819995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.749137379339857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13304970446176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Hollmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40428363128734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.465242131649775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87699793744519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7465237003823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matyas Bauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26623956033117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.632329616148567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.10970797378858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78886120269116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johan Ekberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87110517119952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0553316206665204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.815773550533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jiri Tuz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10820362507409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34320709939847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.680864362015024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77054636245753</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ike Melnits</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00394804884968</t>
+    <t xml:space="preserve">1.71464530281497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexander Ståhlberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49299280422385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Earnhart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47455804041903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.666990490212027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.163921567771262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.977626962859795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeti Pyykko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.546680457582987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OskarOpstad Vike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.432475340986727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161163727163487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dmytro Romanchenko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ukraine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.997935759203038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147570875521796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imanol ROJO GARCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ralf Kivil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gustav Kvarnbrink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yernar NURSBEKOV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juuso VARIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandijs SUHANOVS</t>
   </si>
   <si>
     <t xml:space="preserve">Aleksi Parttimaa</t>
   </si>
   <si>
-    <t xml:space="preserve">OskarOpstad Vike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexander Ståhlberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.442099342589756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federico Pellegrino</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Halfvarsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friedrich Moch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Poromaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edvin Anger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johan Häggström</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elia Barp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jens Burman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beda Klee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valerio Grond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyril Fähndrich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janik Riebli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simone Dapra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francesco De Fabiani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Grate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oskar Svensson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Bögl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davide Graz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Florian Notz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Hellweger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Danielsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paolo Ventura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anian Sossau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janosch Brugger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jiri Tuz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
+    <t xml:space="preserve">Miha Licef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.8687125507133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.30216099962986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.324478275824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.846395274519158</t>
   </si>
   <si>
     <t xml:space="preserve">Tomas Dufek</t>
   </si>
   <si>
-    <t xml:space="preserve">Måns Skoglund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Albert Kuchler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ludek Seller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan Stoelben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Fellner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan-Friedrich Doerks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truls Gisselman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ondrej Cerny</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johan Ekberg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gustav Kvarnbrink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matyas Bauer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veeti Pyykko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.6967092272349</t>
+    <t xml:space="preserve">-1.03501808319774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.232621065824887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.766650795579067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.56904781295192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raimo Vigants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.5817756409166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30531683141162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.16220415961069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.43866296911568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mikayel Mikayelyan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.53902447345779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16867103410246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.138817513850874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.5091709532062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henri Roos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.02742815227766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00522962162342083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.840472378028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.86267090868268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauris Kaparkalejs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.72240141574297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87523067218972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.14241923595094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.98958997950419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Büki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.24501991240203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.05778681123952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentley Walker-Broose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.48324695028333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.44152048384567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nail Bashmakov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.38594518278411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.61647708402643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.99260665689154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.99502892370209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spartak Voskanyan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.81530974350897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08471183889821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.57501326217608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.3056111667868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrej Renda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovakia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.62485695958292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38494595295992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.23871920525471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-12.4786302118777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simeon Deyanov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.86857588517158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.381488428287874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.57335390615778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-12.8234182196172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dmytro Drahun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.26550169517895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.71411563048785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.34392586290516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-13.323543188572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olzhas Klimin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.07577340280702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.4135902522379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.41955615606089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-13.9089198111058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vladislav Kovalyov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.12101413549816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.18458833356103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.97350860009871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.2791110691579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Konya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.04266007237829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.1976128540202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.68287056104776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.9231434874462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seve De Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.15195611409926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.62770263223595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.69490145587212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.4745602022073</t>
   </si>
 </sst>
 </file>
@@ -1011,39 +2085,39 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -1055,514 +2129,514 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.633700227115744</v>
       </c>
       <c r="I11" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.88662311581597</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.88662311581597</v>
       </c>
       <c r="I12" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.853644224416971</v>
       </c>
       <c r="G17" t="s">
-        <v>22</v>
+        <v>93</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.853644224416971</v>
       </c>
       <c r="I17" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.314038160237745</v>
       </c>
       <c r="G19" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0.517761394595505</v>
       </c>
       <c r="I19" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.622459331201855</v>
       </c>
       <c r="G20" t="s">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.517761394595505</v>
       </c>
       <c r="G24" t="s">
-        <v>22</v>
+        <v>124</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.314038160237745</v>
       </c>
       <c r="I24" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.633700227115744</v>
       </c>
       <c r="G25" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0.633700227115744</v>
       </c>
       <c r="I25" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
         <v>22</v>
@@ -1571,85 +2645,85 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0.384358616812558</v>
       </c>
       <c r="I27" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>141</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
@@ -1658,27 +2732,27 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
         <v>22</v>
@@ -1687,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
@@ -1699,44 +2773,44 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>154</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.233125285421556</v>
       </c>
       <c r="G31" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
         <v>22</v>
@@ -1745,39 +2819,39 @@
         <v>0</v>
       </c>
       <c r="E32" t="s">
-        <v>22</v>
+        <v>158</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="D33" t="n">
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>22</v>
+        <v>163</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="s">
         <v>22</v>
@@ -1786,27 +2860,27 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>22</v>
+        <v>167</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="s">
         <v>22</v>
@@ -1815,44 +2889,44 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>170</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>22</v>
+        <v>171</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.152451906798665</v>
       </c>
       <c r="G35" t="s">
-        <v>22</v>
+        <v>172</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.152451906798665</v>
       </c>
       <c r="I35" t="s">
-        <v>22</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="C36" t="s">
         <v>22</v>
@@ -1861,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="s">
         <v>22</v>
@@ -1873,21 +2947,21 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>177</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="s">
         <v>22</v>
@@ -1896,21 +2970,21 @@
         <v>0</v>
       </c>
       <c r="G37" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>22</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
         <v>22</v>
@@ -1919,33 +2993,33 @@
         <v>0</v>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
+        <v>181</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>0.914001122512931</v>
       </c>
       <c r="G38" t="s">
-        <v>22</v>
+        <v>182</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>22</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="s">
         <v>22</v>
@@ -1954,62 +3028,62 @@
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>22</v>
+        <v>186</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>22</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>190</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>191</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>22</v>
+        <v>192</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>22</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="B41" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>195</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="s">
         <v>22</v>
@@ -2018,44 +3092,44 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>22</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>22</v>
+        <v>200</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>22</v>
+        <v>201</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>22</v>
+        <v>202</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
         <v>22</v>
@@ -2064,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>22</v>
+        <v>204</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="s">
         <v>22</v>
@@ -2076,15 +3150,15 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>22</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="C44" t="s">
         <v>22</v>
@@ -2093,27 +3167,27 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>22</v>
+        <v>206</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>22</v>
+        <v>207</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.554369703815855</v>
       </c>
       <c r="I44" t="s">
-        <v>22</v>
+        <v>208</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>135</v>
+        <v>209</v>
       </c>
       <c r="B45" t="s">
-        <v>132</v>
+        <v>210</v>
       </c>
       <c r="C45" t="s">
         <v>22</v>
@@ -2122,62 +3196,62 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>22</v>
+        <v>211</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="s">
-        <v>22</v>
+        <v>212</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>22</v>
+        <v>213</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>136</v>
+        <v>214</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="C46" t="s">
-        <v>22</v>
+        <v>215</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>22</v>
+        <v>216</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.761667602094109</v>
       </c>
       <c r="G46" t="s">
-        <v>22</v>
+        <v>217</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.169951014035129</v>
       </c>
       <c r="I46" t="s">
-        <v>22</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>22</v>
+        <v>220</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="s">
         <v>22</v>
@@ -2186,108 +3260,108 @@
         <v>0</v>
       </c>
       <c r="G47" t="s">
-        <v>22</v>
+        <v>221</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>22</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>138</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>224</v>
       </c>
       <c r="C48" t="s">
-        <v>22</v>
+        <v>225</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>22</v>
+        <v>226</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="s">
-        <v>22</v>
+        <v>227</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>22</v>
+        <v>228</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>139</v>
+        <v>229</v>
       </c>
       <c r="B49" t="s">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="C49" t="s">
-        <v>22</v>
+        <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>22</v>
+        <v>231</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.280201851816773</v>
       </c>
       <c r="G49" t="s">
-        <v>22</v>
+        <v>232</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>0.761667602094109</v>
       </c>
       <c r="I49" t="s">
-        <v>22</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>140</v>
+        <v>234</v>
       </c>
       <c r="B50" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="C50" t="s">
-        <v>22</v>
+        <v>235</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>22</v>
+        <v>236</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.537764103352331</v>
       </c>
       <c r="G50" t="s">
-        <v>22</v>
+        <v>237</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.119991390503082</v>
       </c>
       <c r="I50" t="s">
-        <v>22</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>141</v>
+        <v>239</v>
       </c>
       <c r="B51" t="s">
-        <v>121</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
         <v>22</v>
@@ -2296,56 +3370,56 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>22</v>
+        <v>240</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>0.931618616129238</v>
       </c>
       <c r="G51" t="s">
-        <v>22</v>
+        <v>241</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.931618616129238</v>
       </c>
       <c r="I51" t="s">
-        <v>22</v>
+        <v>242</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>142</v>
+        <v>243</v>
       </c>
       <c r="B52" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>244</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>22</v>
+        <v>245</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>0.0924667556050435</v>
       </c>
       <c r="G52" t="s">
-        <v>22</v>
+        <v>246</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>0.0924667556050435</v>
       </c>
       <c r="I52" t="s">
-        <v>22</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>143</v>
+        <v>248</v>
       </c>
       <c r="B53" t="s">
-        <v>121</v>
+        <v>62</v>
       </c>
       <c r="C53" t="s">
         <v>22</v>
@@ -2354,27 +3428,27 @@
         <v>0</v>
       </c>
       <c r="E53" t="s">
-        <v>22</v>
+        <v>249</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="s">
-        <v>22</v>
+        <v>250</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>22</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>144</v>
+        <v>252</v>
       </c>
       <c r="B54" t="s">
-        <v>123</v>
+        <v>210</v>
       </c>
       <c r="C54" t="s">
         <v>22</v>
@@ -2383,27 +3457,27 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>22</v>
+        <v>253</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="s">
-        <v>22</v>
+        <v>254</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>22</v>
+        <v>255</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>145</v>
+        <v>256</v>
       </c>
       <c r="B55" t="s">
-        <v>121</v>
+        <v>62</v>
       </c>
       <c r="C55" t="s">
         <v>22</v>
@@ -2412,143 +3486,143 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>22</v>
+        <v>257</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="s">
-        <v>22</v>
+        <v>258</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>22</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>146</v>
+        <v>260</v>
       </c>
       <c r="B56" t="s">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>261</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>22</v>
+        <v>262</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>0.461974753179879</v>
       </c>
       <c r="G56" t="s">
-        <v>22</v>
+        <v>263</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.461974753179879</v>
       </c>
       <c r="I56" t="s">
-        <v>22</v>
+        <v>264</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="B57" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="C57" t="s">
-        <v>22</v>
+        <v>266</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>22</v>
+        <v>267</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>0.384358616812558</v>
       </c>
       <c r="G57" t="s">
-        <v>22</v>
+        <v>268</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.233125285421556</v>
       </c>
       <c r="I57" t="s">
-        <v>22</v>
+        <v>269</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>148</v>
+        <v>270</v>
       </c>
       <c r="B58" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>22</v>
+        <v>271</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>22</v>
+        <v>272</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>0.326170416376062</v>
       </c>
       <c r="G58" t="s">
-        <v>22</v>
+        <v>273</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.326170416376062</v>
       </c>
       <c r="I58" t="s">
-        <v>22</v>
+        <v>274</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="B59" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="C59" t="s">
-        <v>22</v>
+        <v>276</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>22</v>
+        <v>277</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>0.190473772503941</v>
       </c>
       <c r="G59" t="s">
-        <v>22</v>
+        <v>278</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>0.190473772503941</v>
       </c>
       <c r="I59" t="s">
-        <v>22</v>
+        <v>279</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>151</v>
+        <v>280</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>36</v>
       </c>
       <c r="C60" t="s">
         <v>22</v>
@@ -2557,27 +3631,27 @@
         <v>0</v>
       </c>
       <c r="E60" t="s">
-        <v>22</v>
+        <v>281</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="s">
-        <v>22</v>
+        <v>282</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60" t="s">
-        <v>22</v>
+        <v>283</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>152</v>
+        <v>284</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="C61" t="s">
         <v>22</v>
@@ -2586,62 +3660,62 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>22</v>
+        <v>285</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G61" t="s">
-        <v>22</v>
+        <v>286</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I61" t="s">
-        <v>22</v>
+        <v>287</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>153</v>
+        <v>288</v>
       </c>
       <c r="B62" t="s">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="C62" t="s">
-        <v>22</v>
+        <v>289</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>22</v>
+        <v>290</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>0.169951014035129</v>
       </c>
       <c r="G62" t="s">
-        <v>22</v>
+        <v>291</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>0.280201851816773</v>
       </c>
       <c r="I62" t="s">
-        <v>22</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>154</v>
+        <v>293</v>
       </c>
       <c r="B63" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>22</v>
+        <v>294</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" t="s">
         <v>22</v>
@@ -2650,33 +3724,33 @@
         <v>0</v>
       </c>
       <c r="G63" t="s">
-        <v>22</v>
+        <v>295</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>155</v>
+        <v>297</v>
       </c>
       <c r="B64" t="s">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>22</v>
+        <v>298</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>22</v>
+        <v>299</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="s">
         <v>22</v>
@@ -2685,73 +3759,73 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>22</v>
+        <v>300</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>156</v>
+        <v>301</v>
       </c>
       <c r="B65" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="C65" t="s">
-        <v>22</v>
+        <v>302</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>22</v>
+        <v>303</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="G65" t="s">
-        <v>22</v>
+        <v>304</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="I65" t="s">
-        <v>22</v>
+        <v>305</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>157</v>
+        <v>306</v>
       </c>
       <c r="B66" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C66" t="s">
-        <v>22</v>
+        <v>307</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>22</v>
+        <v>308</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>0.633700227115744</v>
       </c>
       <c r="G66" t="s">
-        <v>22</v>
+        <v>309</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>0.384358616812558</v>
       </c>
       <c r="I66" t="s">
-        <v>22</v>
+        <v>310</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>158</v>
+        <v>311</v>
       </c>
       <c r="B67" t="s">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="C67" t="s">
         <v>22</v>
@@ -2760,10 +3834,10 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>22</v>
+        <v>312</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="s">
         <v>22</v>
@@ -2772,73 +3846,73 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>22</v>
+        <v>312</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>159</v>
+        <v>313</v>
       </c>
       <c r="B68" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C68" t="s">
-        <v>22</v>
+        <v>314</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>22</v>
+        <v>315</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>0.384358616812558</v>
       </c>
       <c r="G68" t="s">
-        <v>22</v>
+        <v>316</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>0.233125285421556</v>
       </c>
       <c r="I68" t="s">
-        <v>22</v>
+        <v>317</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>160</v>
+        <v>318</v>
       </c>
       <c r="B69" t="s">
-        <v>123</v>
+        <v>50</v>
       </c>
       <c r="C69" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>22</v>
+        <v>320</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="s">
-        <v>22</v>
+        <v>321</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" t="s">
-        <v>22</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>161</v>
+        <v>323</v>
       </c>
       <c r="B70" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="C70" t="s">
         <v>22</v>
@@ -2847,48 +3921,1403 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>22</v>
+        <v>324</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>0.554369703815855</v>
       </c>
       <c r="G70" t="s">
-        <v>22</v>
+        <v>325</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>0.914001122512931</v>
       </c>
       <c r="I70" t="s">
-        <v>22</v>
+        <v>326</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>162</v>
+        <v>327</v>
       </c>
       <c r="B71" t="s">
+        <v>62</v>
+      </c>
+      <c r="C71" t="s">
+        <v>328</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="s">
+        <v>329</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.197832357823317</v>
+      </c>
+      <c r="G71" t="s">
+        <v>330</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.537764103352331</v>
+      </c>
+      <c r="I71" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>332</v>
+      </c>
+      <c r="B72" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" t="s">
+        <v>333</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="s">
+        <v>334</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.115528182894769</v>
+      </c>
+      <c r="G72" t="s">
+        <v>335</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.115528182894769</v>
+      </c>
+      <c r="I72" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>337</v>
+      </c>
+      <c r="B73" t="s">
+        <v>338</v>
+      </c>
+      <c r="C73" t="s">
+        <v>339</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
+        <v>340</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="s">
+        <v>341</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="I73" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>343</v>
+      </c>
+      <c r="B74" t="s">
+        <v>62</v>
+      </c>
+      <c r="C74" t="s">
+        <v>344</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
+        <v>345</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.119991390503082</v>
+      </c>
+      <c r="G74" t="s">
+        <v>346</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.197832357823317</v>
+      </c>
+      <c r="I74" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>348</v>
+      </c>
+      <c r="B75" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" t="s">
+        <v>349</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>22</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="s">
+        <v>212</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>351</v>
+      </c>
+      <c r="B76" t="s">
+        <v>352</v>
+      </c>
+      <c r="C76" t="s">
+        <v>353</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>354</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="s">
+        <v>355</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>357</v>
+      </c>
+      <c r="B77" t="s">
+        <v>56</v>
+      </c>
+      <c r="C77" t="s">
+        <v>358</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="s">
+        <v>359</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.141397633162432</v>
+      </c>
+      <c r="G77" t="s">
+        <v>360</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>362</v>
+      </c>
+      <c r="B78" t="s">
+        <v>210</v>
+      </c>
+      <c r="C78" t="s">
+        <v>363</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
+        <v>364</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.910108467846823</v>
+      </c>
+      <c r="G78" t="s">
+        <v>365</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.203072648183104</v>
+      </c>
+      <c r="I78" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>367</v>
+      </c>
+      <c r="B79" t="s">
+        <v>368</v>
+      </c>
+      <c r="C79" t="s">
+        <v>369</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="s">
+        <v>370</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="s">
+        <v>371</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>373</v>
+      </c>
+      <c r="B80" t="s">
         <v>26</v>
       </c>
-      <c r="C71" t="s">
-        <v>22</v>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="s">
-        <v>22</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="s">
-        <v>163</v>
-      </c>
-      <c r="H71" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" t="s">
-        <v>163</v>
+      <c r="C80" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="s">
+        <v>374</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>375</v>
+      </c>
+      <c r="B81" t="s">
+        <v>368</v>
+      </c>
+      <c r="C81" t="s">
+        <v>376</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="s">
+        <v>377</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="s">
+        <v>378</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>380</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="s">
+        <v>22</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="s">
+        <v>381</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>382</v>
+      </c>
+      <c r="B83" t="s">
+        <v>90</v>
+      </c>
+      <c r="C83" t="s">
+        <v>22</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="s">
+        <v>383</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.336242222180128</v>
+      </c>
+      <c r="G83" t="s">
+        <v>384</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.336242222180128</v>
+      </c>
+      <c r="I83" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>386</v>
+      </c>
+      <c r="B84" t="s">
+        <v>74</v>
+      </c>
+      <c r="C84" t="s">
+        <v>387</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="s">
+        <v>359</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.141397633162432</v>
+      </c>
+      <c r="G84" t="s">
+        <v>388</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.141397633162432</v>
+      </c>
+      <c r="I84" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>390</v>
+      </c>
+      <c r="B85" t="s">
+        <v>50</v>
+      </c>
+      <c r="C85" t="s">
+        <v>391</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="s">
+        <v>392</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.406145296366207</v>
+      </c>
+      <c r="G85" t="s">
+        <v>393</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.669620389113773</v>
+      </c>
+      <c r="I85" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>395</v>
+      </c>
+      <c r="B86" t="s">
+        <v>210</v>
+      </c>
+      <c r="C86" t="s">
+        <v>396</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="s">
+        <v>397</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.552008689413187</v>
+      </c>
+      <c r="G86" t="s">
+        <v>398</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.910108467846823</v>
+      </c>
+      <c r="I86" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>400</v>
+      </c>
+      <c r="B87" t="s">
+        <v>90</v>
+      </c>
+      <c r="C87" t="s">
+        <v>22</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="s">
+        <v>401</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.203941216842155</v>
+      </c>
+      <c r="G87" t="s">
+        <v>402</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.203941216842155</v>
+      </c>
+      <c r="I87" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>404</v>
+      </c>
+      <c r="B88" t="s">
+        <v>210</v>
+      </c>
+      <c r="C88" t="s">
+        <v>405</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="s">
+        <v>406</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.334810194556887</v>
+      </c>
+      <c r="G88" t="s">
+        <v>407</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.552008689413187</v>
+      </c>
+      <c r="I88" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>409</v>
+      </c>
+      <c r="B89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" t="s">
+        <v>22</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="s">
+        <v>410</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="s">
+        <v>22</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>411</v>
+      </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" t="s">
+        <v>412</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="s">
+        <v>22</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="s">
+        <v>22</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>413</v>
+      </c>
+      <c r="B91" t="s">
+        <v>56</v>
+      </c>
+      <c r="C91" t="s">
+        <v>414</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="s">
+        <v>415</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.233125285421556</v>
+      </c>
+      <c r="G91" t="s">
+        <v>416</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.141397633162432</v>
+      </c>
+      <c r="I91" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>418</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" t="s">
+        <v>22</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="s">
+        <v>22</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="s">
+        <v>419</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>420</v>
+      </c>
+      <c r="B93" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" t="s">
+        <v>22</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="s">
+        <v>421</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.377540668798145</v>
+      </c>
+      <c r="G93" t="s">
+        <v>212</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>423</v>
+      </c>
+      <c r="B94" t="s">
+        <v>424</v>
+      </c>
+      <c r="C94" t="s">
+        <v>425</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="s">
+        <v>354</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="s">
+        <v>22</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>427</v>
+      </c>
+      <c r="B95"/>
+      <c r="C95" t="s">
+        <v>298</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="s">
+        <v>22</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="s">
+        <v>22</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>428</v>
+      </c>
+      <c r="B96" t="s">
+        <v>368</v>
+      </c>
+      <c r="C96" t="s">
+        <v>298</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="s">
+        <v>22</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="s">
+        <v>22</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>429</v>
+      </c>
+      <c r="B97" t="s">
+        <v>90</v>
+      </c>
+      <c r="C97" t="s">
+        <v>298</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="s">
+        <v>22</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="s">
+        <v>22</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>430</v>
+      </c>
+      <c r="B98"/>
+      <c r="C98" t="s">
+        <v>298</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="s">
+        <v>22</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="s">
+        <v>22</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>431</v>
+      </c>
+      <c r="B99"/>
+      <c r="C99" t="s">
+        <v>298</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="s">
+        <v>22</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>432</v>
+      </c>
+      <c r="B100"/>
+      <c r="C100" t="s">
+        <v>298</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="s">
+        <v>22</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="s">
+        <v>22</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>433</v>
+      </c>
+      <c r="B101" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" t="s">
+        <v>22</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="s">
+        <v>22</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="s">
+        <v>212</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>434</v>
+      </c>
+      <c r="B102" t="s">
+        <v>338</v>
+      </c>
+      <c r="C102" t="s">
+        <v>435</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="s">
+        <v>436</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="G102" t="s">
+        <v>437</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>439</v>
+      </c>
+      <c r="B103" t="s">
+        <v>210</v>
+      </c>
+      <c r="C103" t="s">
+        <v>440</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="s">
+        <v>441</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.203072648183104</v>
+      </c>
+      <c r="G103" t="s">
+        <v>442</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.334810194556887</v>
+      </c>
+      <c r="I103" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>444</v>
+      </c>
+      <c r="B104" t="s">
+        <v>445</v>
+      </c>
+      <c r="C104" t="s">
+        <v>446</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="s">
+        <v>447</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="G104" t="s">
+        <v>448</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="I104" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>450</v>
+      </c>
+      <c r="B105" t="s">
+        <v>451</v>
+      </c>
+      <c r="C105" t="s">
+        <v>452</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="s">
+        <v>453</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="G105" t="s">
+        <v>454</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="I105" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>456</v>
+      </c>
+      <c r="B106" t="s">
+        <v>368</v>
+      </c>
+      <c r="C106" t="s">
+        <v>457</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="s">
+        <v>458</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.74529489290339</v>
+      </c>
+      <c r="G106" t="s">
+        <v>459</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.74529489290339</v>
+      </c>
+      <c r="I106" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>461</v>
+      </c>
+      <c r="B107" t="s">
+        <v>445</v>
+      </c>
+      <c r="C107" t="s">
+        <v>462</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="s">
+        <v>463</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="s">
+        <v>464</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>466</v>
+      </c>
+      <c r="B108" t="s">
+        <v>467</v>
+      </c>
+      <c r="C108" t="s">
+        <v>298</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="s">
+        <v>354</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="s">
+        <v>468</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>470</v>
+      </c>
+      <c r="B109" t="s">
+        <v>471</v>
+      </c>
+      <c r="C109" t="s">
+        <v>298</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="s">
+        <v>22</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="s">
+        <v>472</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>474</v>
+      </c>
+      <c r="B110" t="s">
+        <v>475</v>
+      </c>
+      <c r="C110" t="s">
+        <v>476</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="s">
+        <v>477</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="s">
+        <v>478</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.921587657155495</v>
+      </c>
+      <c r="I110" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>480</v>
+      </c>
+      <c r="B111" t="s">
+        <v>451</v>
+      </c>
+      <c r="C111" t="s">
+        <v>481</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="s">
+        <v>482</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="s">
+        <v>483</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>485</v>
+      </c>
+      <c r="B112" t="s">
+        <v>486</v>
+      </c>
+      <c r="C112" t="s">
+        <v>487</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="s">
+        <v>488</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" t="s">
+        <v>489</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>491</v>
+      </c>
+      <c r="B113" t="s">
+        <v>492</v>
+      </c>
+      <c r="C113" t="s">
+        <v>493</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="s">
+        <v>494</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="s">
+        <v>495</v>
+      </c>
+      <c r="H113" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>497</v>
+      </c>
+      <c r="B114" t="s">
+        <v>424</v>
+      </c>
+      <c r="C114" t="s">
+        <v>498</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="s">
+        <v>499</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="G114" t="s">
+        <v>500</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>502</v>
+      </c>
+      <c r="B115" t="s">
+        <v>475</v>
+      </c>
+      <c r="C115" t="s">
+        <v>503</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="s">
+        <v>504</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.921587657155495</v>
+      </c>
+      <c r="G115" t="s">
+        <v>505</v>
+      </c>
+      <c r="H115" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>507</v>
+      </c>
+      <c r="B116" t="s">
+        <v>475</v>
+      </c>
+      <c r="C116" t="s">
+        <v>508</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="s">
+        <v>509</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.558971169677543</v>
+      </c>
+      <c r="G116" t="s">
+        <v>510</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.558971169677543</v>
+      </c>
+      <c r="I116" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>512</v>
+      </c>
+      <c r="B117" t="s">
+        <v>467</v>
+      </c>
+      <c r="C117" t="s">
+        <v>513</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="s">
+        <v>514</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="G117" t="s">
+        <v>515</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="I117" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>517</v>
+      </c>
+      <c r="B118" t="s">
+        <v>471</v>
+      </c>
+      <c r="C118" t="s">
+        <v>518</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="s">
+        <v>519</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" t="s">
+        <v>520</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.755081337596291</v>
+      </c>
+      <c r="I118" t="s">
+        <v>521</v>
       </c>
     </row>
   </sheetData>

--- a/content/post/drafts/weekly-picks/2025Ruka/men-points.xlsx
+++ b/content/post/drafts/weekly-picks/2025Ruka/men-points.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="526">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -179,6 +179,24 @@
     <t xml:space="preserve">112.960953556265</t>
   </si>
   <si>
+    <t xml:space="preserve">Calle Halfvarsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0581301340895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9119748060865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.779670970042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.749775910218</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ben Ogden</t>
   </si>
   <si>
@@ -197,6 +215,24 @@
     <t xml:space="preserve">109.660736466014</t>
   </si>
   <si>
+    <t xml:space="preserve">Mika Vermeulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0592431478938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66960430357104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9446284316745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.673475883139</t>
+  </si>
+  <si>
     <t xml:space="preserve">Friedrich Moch</t>
   </si>
   <si>
@@ -206,31 +242,28 @@
     <t xml:space="preserve">44.9930008669976</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81518586850096</t>
+    <t xml:space="preserve">3.24292565112653</t>
   </si>
   <si>
     <t xml:space="preserve">54.8713570839061</t>
   </si>
   <si>
-    <t xml:space="preserve">108.679543819405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mika Vermeulen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0592431478938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66960430357104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9446284316745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.673475883139</t>
+    <t xml:space="preserve">103.10728360203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Iversen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.8550371809275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3374018477558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2238421853649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.416281214048</t>
   </si>
   <si>
     <t xml:space="preserve">Hugo Lapalus</t>
@@ -242,28 +275,13 @@
     <t xml:space="preserve">41.2868956787035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83557776217343</t>
+    <t xml:space="preserve">0.912604462128752</t>
   </si>
   <si>
     <t xml:space="preserve">57.1097520898675</t>
   </si>
   <si>
-    <t xml:space="preserve">102.232225530744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Iversen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.8550371809275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3374018477558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.2238421853649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.416281214048</t>
+    <t xml:space="preserve">99.3092522306997</t>
   </si>
   <si>
     <t xml:space="preserve">Gus Schumacher</t>
@@ -281,52 +299,34 @@
     <t xml:space="preserve">99.1036306512329</t>
   </si>
   <si>
+    <t xml:space="preserve">Lauri Vuorinen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.476494621768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4573937156602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50236726598532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4362556034135</t>
+  </si>
+  <si>
     <t xml:space="preserve">William Poromaa</t>
   </si>
   <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
     <t xml:space="preserve">42.7352091122971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3510715994482</t>
+    <t xml:space="preserve">2.30963626369275</t>
   </si>
   <si>
     <t xml:space="preserve">40.6146172157061</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7008979274514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauri Vuorinen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.476494621768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4573937156602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50236726598532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4362556034135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Halfvarsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0581301340895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0506744288832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.779670970042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.8884755330148</t>
+    <t xml:space="preserve">85.6594625916959</t>
   </si>
   <si>
     <t xml:space="preserve">Jan Thomas Jenssen</t>
@@ -341,19 +341,49 @@
     <t xml:space="preserve">83.2063286295823</t>
   </si>
   <si>
+    <t xml:space="preserve">Richard Jouve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3085398187634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6322886454464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5339551074586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4747835716685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jules Chappaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.627431124463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9316569691673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3661182789358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.9252063725662</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jules Lapierre</t>
   </si>
   <si>
     <t xml:space="preserve">20.8834788909157</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96542420645009</t>
+    <t xml:space="preserve">1.55556688824092</t>
   </si>
   <si>
     <t xml:space="preserve">49.32834330695</t>
   </si>
   <si>
-    <t xml:space="preserve">74.1772464043158</t>
+    <t xml:space="preserve">71.7673890861066</t>
   </si>
   <si>
     <t xml:space="preserve">Francesco De Fabiani</t>
@@ -383,28 +413,13 @@
     <t xml:space="preserve">45.919675156865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90636108232244</t>
+    <t xml:space="preserve">0.8716269738962</t>
   </si>
   <si>
     <t xml:space="preserve">16.0317635069991</t>
   </si>
   <si>
-    <t xml:space="preserve">65.8577997461865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richard Jouve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3085398187634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.3530932682408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5339551074586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1955881944628</t>
+    <t xml:space="preserve">62.8230656377603</t>
   </si>
   <si>
     <t xml:space="preserve">Johan Häggström</t>
@@ -434,67 +449,52 @@
     <t xml:space="preserve">59.097766617816</t>
   </si>
   <si>
+    <t xml:space="preserve">Valerio Grond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7447917881014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60908168097862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.35387346908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Håvard Solås Taugbøl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4285711808128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joni Mäki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.429606160483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36077004354031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7903762040233</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zanden McMullen</t>
   </si>
   <si>
     <t xml:space="preserve">14.9474410946987</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7376942661655</t>
+    <t xml:space="preserve">15.9994662839916</t>
   </si>
   <si>
     <t xml:space="preserve">17.78442723455</t>
   </si>
   <si>
-    <t xml:space="preserve">57.4695625954142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valerio Grond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7447917881014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60908168097862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.35387346908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Håvard Solås Taugbøl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4285711808128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jules Chappaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.627431124463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44407664492036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3661182789358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4376260483192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joni Mäki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.429606160483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36077004354031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7903762040233</t>
+    <t xml:space="preserve">48.7313346132403</t>
   </si>
   <si>
     <t xml:space="preserve">Ristomatti Hakola</t>
@@ -521,19 +521,31 @@
     <t xml:space="preserve">43.9219175109499</t>
   </si>
   <si>
+    <t xml:space="preserve">Marcus Grate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.42514969696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.85101791438463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5741317825753</t>
+  </si>
+  <si>
     <t xml:space="preserve">Beda Klee</t>
   </si>
   <si>
     <t xml:space="preserve">36.0087660412692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.05131574408386</t>
+    <t xml:space="preserve">0.63765523182546</t>
   </si>
   <si>
     <t xml:space="preserve">4.76347216839213</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8235539537452</t>
+    <t xml:space="preserve">41.4098934414868</t>
   </si>
   <si>
     <t xml:space="preserve">Sivert Wiig</t>
@@ -554,18 +566,6 @@
     <t xml:space="preserve">40.2327539025056</t>
   </si>
   <si>
-    <t xml:space="preserve">Marcus Grate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.6046366908264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.85101791438463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7536187764418</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arsi Ruuskanen</t>
   </si>
   <si>
@@ -578,6 +578,21 @@
     <t xml:space="preserve">38.2435194026346</t>
   </si>
   <si>
+    <t xml:space="preserve">Edvin Anger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63852059707695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4196328080105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07405838288122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1322117879687</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thomas Hjalmar Westgård</t>
   </si>
   <si>
@@ -629,58 +644,91 @@
     <t xml:space="preserve">33.4595909446622</t>
   </si>
   <si>
+    <t xml:space="preserve">0.145374899161503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.6049658438237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davide Graz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18873996743786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56245332401654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3290024732266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.080195764681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondrej Cerny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.0234744538969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.27131161382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7521628400737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elia Barp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9164653781413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3318269736354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30576208283771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5540544346144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Markus Vuorela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7256607093068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2691480279229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9948087372297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan Stoelben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1454967513713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28404786365813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4295446150294</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oskar Svensson</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4233173789274</t>
+    <t xml:space="preserve">29.6349484799327</t>
   </si>
   <si>
     <t xml:space="preserve">-0.796277264146794</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6270401147806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ondrej Cerny</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.0234744538969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.27131161382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7521628400737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elia Barp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9164653781413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3318269736354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30576208283771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5540544346144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Markus Vuorela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7256607093068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2691480279229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9948087372297</t>
+    <t xml:space="preserve">28.8386712157859</t>
   </si>
   <si>
     <t xml:space="preserve">Irineu Esteve Altimiras</t>
@@ -701,19 +749,19 @@
     <t xml:space="preserve">28.7201717926568</t>
   </si>
   <si>
-    <t xml:space="preserve">Davide Graz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18873996743786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19339046337438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3290024732266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7111329040389</t>
+    <t xml:space="preserve">Cyril Fähndrich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2438721074186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95987919935189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04164317861658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.245394485387</t>
   </si>
   <si>
     <t xml:space="preserve">Albert Kuchler</t>
@@ -722,52 +770,70 @@
     <t xml:space="preserve">25.7315264013895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.17761636440912</t>
+    <t xml:space="preserve">0.433220850053171</t>
   </si>
   <si>
     <t xml:space="preserve">1.15767748609493</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0668202518935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan Stoelben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2892501176532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28404786365813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5732979813114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyril Fähndrich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2438721074186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18872682373997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04164317861658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4742421097751</t>
+    <t xml:space="preserve">27.3224247375376</t>
   </si>
   <si>
     <t xml:space="preserve">Florian Notz</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726232422949847</t>
+    <t xml:space="preserve">0.67657164485672</t>
   </si>
   <si>
     <t xml:space="preserve">26.392450255265</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1186826782149</t>
+    <t xml:space="preserve">27.0690219001217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remi Bourdin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9945602001411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5990886774708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75182456018424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3454734377961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Janosch Brugger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.196468825082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64596764636728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11774855596486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9601850274142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zak Ketterson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31153480451816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5484269310004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31345256601208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1734143015306</t>
   </si>
   <si>
     <t xml:space="preserve">Ludek Seller</t>
@@ -800,58 +866,13 @@
     <t xml:space="preserve">11.2959375901972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90910608212722</t>
+    <t xml:space="preserve">1.15793137145402</t>
   </si>
   <si>
     <t xml:space="preserve">8.77471660591621</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9797602782406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remi Bourdin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9945602001411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89309418761832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75182456018424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6394789479436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Janosch Brugger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.196468825082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81279430496052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11774855596486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1270116860074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edvin Anger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63852059707695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0871191945371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07405838288122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7996981744952</t>
+    <t xml:space="preserve">21.2285855675674</t>
   </si>
   <si>
     <t xml:space="preserve">Michael Hellweger</t>
@@ -878,6 +899,21 @@
     <t xml:space="preserve">20.1392584861006</t>
   </si>
   <si>
+    <t xml:space="preserve">Xavier McKeever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98652929361133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3997640588749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.599609933115996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9859032856022</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paolo Ventura</t>
   </si>
   <si>
@@ -917,19 +953,43 @@
     <t xml:space="preserve">16.2040422657233</t>
   </si>
   <si>
-    <t xml:space="preserve">Xavier McKeever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98652929361133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30313483402279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.599609933115996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8892740607501</t>
+    <t xml:space="preserve">Wiljam Mattila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0962922005034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0314554792847596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1277476797882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emil Danielsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.842309343126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.42609894337061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4162103997554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truls Gisselman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7489442356172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33358781038181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.14402102068428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2265530666833</t>
   </si>
   <si>
     <t xml:space="preserve">Hunter Wonders</t>
@@ -938,34 +998,28 @@
     <t xml:space="preserve">9.69584305150782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90225465333071</t>
+    <t xml:space="preserve">0.714227533515729</t>
   </si>
   <si>
     <t xml:space="preserve">3.75557612139249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.353673826231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiljam Mattila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0962922005034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zak Ketterson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31153480451816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36053048562298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31345256601208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9855178561532</t>
+    <t xml:space="preserve">14.165646706416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucas Bögl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00783485710589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.318515587801453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35057459055772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6769250354651</t>
   </si>
   <si>
     <t xml:space="preserve">Olivier Leveille</t>
@@ -974,55 +1028,28 @@
     <t xml:space="preserve">5.93900500726964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88047004834322</t>
+    <t xml:space="preserve">1.16988936145834</t>
   </si>
   <si>
     <t xml:space="preserve">5.85569582890601</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6751708845189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emil Danielsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.842309343126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.42609894337061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4162103997554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucas Bögl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00783485710589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52514342465781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35057459055772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8835528723214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truls Gisselman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7489442356172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59423786195063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.14402102068428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4872031182521</t>
+    <t xml:space="preserve">12.964590197634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan-Friedrich Doerks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22890739757373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782641429414709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.966284623020501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9778334500089</t>
   </si>
   <si>
     <t xml:space="preserve">Miha Simenc</t>
@@ -1043,21 +1070,6 @@
     <t xml:space="preserve">10.6777957110915</t>
   </si>
   <si>
-    <t xml:space="preserve">Jan-Friedrich Doerks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22890739757373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1746309074841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.966284623020501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3698229280783</t>
-  </si>
-  <si>
     <t xml:space="preserve">Andreas Fjorden Ree</t>
   </si>
   <si>
@@ -1076,13 +1088,10 @@
     <t xml:space="preserve">-0.734936766045822</t>
   </si>
   <si>
-    <t xml:space="preserve">1.14550663472483</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.12614022329822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53671009197723</t>
+    <t xml:space="preserve">8.3912034572524</t>
   </si>
   <si>
     <t xml:space="preserve">Johnny Hagenbuch</t>
@@ -1091,13 +1100,28 @@
     <t xml:space="preserve">-0.326951575906619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161971926921955</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.69645538965557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53147574067091</t>
+    <t xml:space="preserve">8.36950381374895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvar Johannes Alev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.132098055202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.836845989550548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20198326607999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49723533173144</t>
   </si>
   <si>
     <t xml:space="preserve">Adam Fellner</t>
@@ -1106,31 +1130,28 @@
     <t xml:space="preserve">4.52492987561916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14914235386252</t>
+    <t xml:space="preserve">1.28942856608742</t>
   </si>
   <si>
     <t xml:space="preserve">0.636790238963534</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31086246844521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alvar Johannes Alev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.132098055202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.836845989550548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20198326607999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49723533173144</t>
+    <t xml:space="preserve">6.45114868067011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jiri Tuz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10820362507409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99861335614241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.680864362015024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42595261920148</t>
   </si>
   <si>
     <t xml:space="preserve">Eero Rantala</t>
@@ -1139,6 +1160,12 @@
     <t xml:space="preserve">6.11588473260095</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.0275479839509585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08833674865</t>
+  </si>
+  <si>
     <t xml:space="preserve">Martin Himma</t>
   </si>
   <si>
@@ -1172,6 +1199,21 @@
     <t xml:space="preserve">5.10681364781495</t>
   </si>
   <si>
+    <t xml:space="preserve">Max Hollmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40428363128734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.767054598476853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87699793744519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04833616720938</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mathis Desloges</t>
   </si>
   <si>
@@ -1181,22 +1223,7 @@
     <t xml:space="preserve">0.749137379339857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13304970446176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Hollmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40428363128734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.465242131649775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87699793744519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7465237003823</t>
+    <t xml:space="preserve">3.97107777753981</t>
   </si>
   <si>
     <t xml:space="preserve">Matyas Bauer</t>
@@ -1205,13 +1232,13 @@
     <t xml:space="preserve">2.26623956033117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632329616148567</t>
+    <t xml:space="preserve">0.703789850501424</t>
   </si>
   <si>
     <t xml:space="preserve">-0.10970797378858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78886120269116</t>
+    <t xml:space="preserve">2.86032143704402</t>
   </si>
   <si>
     <t xml:space="preserve">Johan Ekberg</t>
@@ -1226,27 +1253,18 @@
     <t xml:space="preserve">1.815773550533</t>
   </si>
   <si>
-    <t xml:space="preserve">Jiri Tuz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10820362507409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34320709939847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.680864362015024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77054636245753</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ike Melnits</t>
   </si>
   <si>
     <t xml:space="preserve">1.71464530281497</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.045418947104851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66922635571012</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alexander Ståhlberg</t>
   </si>
   <si>
@@ -1259,13 +1277,13 @@
     <t xml:space="preserve">0.47455804041903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666990490212027</t>
+    <t xml:space="preserve">1.12235255059994</t>
   </si>
   <si>
     <t xml:space="preserve">-0.163921567771262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.977626962859795</t>
+    <t xml:space="preserve">1.43298902324771</t>
   </si>
   <si>
     <t xml:space="preserve">Veeti Pyykko</t>
@@ -1283,6 +1301,48 @@
     <t xml:space="preserve">0.161163727163487</t>
   </si>
   <si>
+    <t xml:space="preserve">Imanol ROJO GARCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gustav Kvarnbrink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juuso Varis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ralf Kivil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yernar Nursbekov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandijs Suhanovs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aleksi Parttimaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miha Licef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.8687125507133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.30216099962986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.324478275824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.846395274519158</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dmytro Romanchenko</t>
   </si>
   <si>
@@ -1292,76 +1352,31 @@
     <t xml:space="preserve">-0.997935759203038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147570875521796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imanol ROJO GARCIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ralf Kivil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gustav Kvarnbrink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yernar NURSBEKOV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juuso VARIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandijs SUHANOVS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aleksi Parttimaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Licef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.8687125507133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.30216099962986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.324478275824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.846395274519158</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tomas Dufek</t>
   </si>
   <si>
     <t xml:space="preserve">-1.03501808319774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232621065824887</t>
-  </si>
-  <si>
     <t xml:space="preserve">-0.766650795579067</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.56904781295192</t>
+    <t xml:space="preserve">-1.8016688787768</t>
   </si>
   <si>
     <t xml:space="preserve">Raimo Vigants</t>
   </si>
   <si>
-    <t xml:space="preserve">Latvia</t>
-  </si>
-  <si>
     <t xml:space="preserve">-5.5817756409166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30531683141162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.16220415961069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.43866296911568</t>
+    <t xml:space="preserve">4.37743149888155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.53917743922851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.74352158126356</t>
   </si>
   <si>
     <t xml:space="preserve">Mikayel Mikayelyan</t>
@@ -1412,6 +1427,33 @@
     <t xml:space="preserve">-6.98958997950419</t>
   </si>
   <si>
+    <t xml:space="preserve">Bentley Walker-Broose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.48324695028333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.44152048384567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nail Bashmakov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.38594518278411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.61647708402643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.1621455554665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.16456782227705</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adam Büki</t>
   </si>
   <si>
@@ -1421,37 +1463,7 @@
     <t xml:space="preserve">-9.24501991240203</t>
   </si>
   <si>
-    <t xml:space="preserve">-8.05778681123952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bentley Walker-Broose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.48324695028333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.44152048384567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nail Bashmakov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kazakhstan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.38594518278411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.61647708402643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.99260665689154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.99502892370209</t>
+    <t xml:space="preserve">-9.20329344596436</t>
   </si>
   <si>
     <t xml:space="preserve">Spartak Voskanyan</t>
@@ -1511,13 +1523,13 @@
     <t xml:space="preserve">-4.26550169517895</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.71411563048785</t>
+    <t xml:space="preserve">-2.27010726545637</t>
   </si>
   <si>
     <t xml:space="preserve">-7.34392586290516</t>
   </si>
   <si>
-    <t xml:space="preserve">-13.323543188572</t>
+    <t xml:space="preserve">-13.8795348235405</t>
   </si>
   <si>
     <t xml:space="preserve">Olzhas Klimin</t>
@@ -1526,13 +1538,28 @@
     <t xml:space="preserve">-5.07577340280702</t>
   </si>
   <si>
-    <t xml:space="preserve">-2.4135902522379</t>
+    <t xml:space="preserve">-2.61894810927428</t>
   </si>
   <si>
     <t xml:space="preserve">-6.41955615606089</t>
   </si>
   <si>
-    <t xml:space="preserve">-13.9089198111058</t>
+    <t xml:space="preserve">-14.1142776681422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Konya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.04266007237829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.91043195560366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.68287056104776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-15.6359625890297</t>
   </si>
   <si>
     <t xml:space="preserve">Vladislav Kovalyov</t>
@@ -1541,28 +1568,13 @@
     <t xml:space="preserve">-8.12101413549816</t>
   </si>
   <si>
-    <t xml:space="preserve">-2.18458833356103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.97350860009871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.2791110691579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Konya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.04266007237829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.1976128540202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.68287056104776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.9231434874462</t>
+    <t xml:space="preserve">-2.91278444474804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.29801146679828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.3318100470445</t>
   </si>
   <si>
     <t xml:space="preserve">Seve De Campo</t>
@@ -2213,13 +2225,13 @@
         <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.853644224416971</v>
       </c>
       <c r="G11" t="s">
         <v>59</v>
       </c>
       <c r="H11" t="n">
-        <v>0.633700227115744</v>
+        <v>0.517761394595505</v>
       </c>
       <c r="I11" t="s">
         <v>60</v>
@@ -2242,13 +2254,13 @@
         <v>64</v>
       </c>
       <c r="F12" t="n">
-        <v>0.88662311581597</v>
+        <v>1</v>
       </c>
       <c r="G12" t="s">
         <v>65</v>
       </c>
       <c r="H12" t="n">
-        <v>0.88662311581597</v>
+        <v>0.633700227115744</v>
       </c>
       <c r="I12" t="s">
         <v>66</v>
@@ -2300,13 +2312,13 @@
         <v>76</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.326170416376062</v>
       </c>
       <c r="G14" t="s">
         <v>77</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.88662311581597</v>
       </c>
       <c r="I14" t="s">
         <v>78</v>
@@ -2346,36 +2358,36 @@
         <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.237931419649181</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
         <v>91</v>
@@ -2387,13 +2399,13 @@
         <v>92</v>
       </c>
       <c r="F17" t="n">
-        <v>0.853644224416971</v>
+        <v>1</v>
       </c>
       <c r="G17" t="s">
         <v>93</v>
       </c>
       <c r="H17" t="n">
-        <v>0.853644224416971</v>
+        <v>1</v>
       </c>
       <c r="I17" t="s">
         <v>94</v>
@@ -2433,7 +2445,7 @@
         <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
         <v>101</v>
@@ -2445,13 +2457,13 @@
         <v>102</v>
       </c>
       <c r="F19" t="n">
-        <v>0.314038160237745</v>
+        <v>0.190473772503941</v>
       </c>
       <c r="G19" t="s">
         <v>103</v>
       </c>
       <c r="H19" t="n">
-        <v>0.517761394595505</v>
+        <v>0.853644224416971</v>
       </c>
       <c r="I19" t="s">
         <v>104</v>
@@ -2491,7 +2503,7 @@
         <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
         <v>110</v>
@@ -2509,7 +2521,7 @@
         <v>112</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0.633700227115744</v>
       </c>
       <c r="I21" t="s">
         <v>113</v>
@@ -2520,7 +2532,7 @@
         <v>114</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
         <v>115</v>
@@ -2549,83 +2561,83 @@
         <v>119</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0.392282592543483</v>
       </c>
       <c r="G23" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F24" t="n">
-        <v>0.517761394595505</v>
+        <v>1</v>
       </c>
       <c r="G24" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H24" t="n">
-        <v>0.314038160237745</v>
+        <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F25" t="n">
-        <v>0.633700227115744</v>
+        <v>1</v>
       </c>
       <c r="G25" t="s">
-        <v>129</v>
+        <v>22</v>
       </c>
       <c r="H25" t="n">
-        <v>0.633700227115744</v>
+        <v>0</v>
       </c>
       <c r="I25" t="s">
         <v>130</v>
@@ -2636,42 +2648,42 @@
         <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.115528182894769</v>
       </c>
       <c r="G26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0.314038160237745</v>
       </c>
       <c r="I26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="s">
         <v>137</v>
@@ -2683,7 +2695,7 @@
         <v>138</v>
       </c>
       <c r="H27" t="n">
-        <v>0.384358616812558</v>
+        <v>1</v>
       </c>
       <c r="I27" t="s">
         <v>139</v>
@@ -2694,7 +2706,7 @@
         <v>140</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
         <v>141</v>
@@ -2712,7 +2724,7 @@
         <v>143</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0.384358616812558</v>
       </c>
       <c r="I28" t="s">
         <v>144</v>
@@ -2781,48 +2793,48 @@
         <v>152</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
         <v>153</v>
       </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
         <v>154</v>
       </c>
-      <c r="F31" t="n">
-        <v>0.233125285421556</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
         <v>155</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>156</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
         <v>157</v>
       </c>
-      <c r="B32" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" t="s">
-        <v>22</v>
-      </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="s">
         <v>158</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.646764654451831</v>
       </c>
       <c r="G32" t="s">
         <v>159</v>
@@ -2897,83 +2909,83 @@
         <v>169</v>
       </c>
       <c r="B35" t="s">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
         <v>170</v>
       </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
         <v>171</v>
       </c>
-      <c r="F35" t="n">
-        <v>0.152451906798665</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
         <v>172</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.152451906798665</v>
-      </c>
-      <c r="I35" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>173</v>
+      </c>
+      <c r="B36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C36" t="s">
         <v>174</v>
       </c>
-      <c r="B36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" t="s">
-        <v>22</v>
-      </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" t="s">
         <v>175</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0.0924667556050435</v>
       </c>
       <c r="G36" t="s">
-        <v>22</v>
+        <v>176</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.152451906798665</v>
       </c>
       <c r="I36" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
+        <v>22</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>22</v>
+        <v>179</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>178</v>
+        <v>22</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="s">
         <v>179</v>
@@ -2984,19 +2996,19 @@
         <v>180</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>181</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>181</v>
+        <v>22</v>
       </c>
       <c r="F38" t="n">
-        <v>0.914001122512931</v>
+        <v>0</v>
       </c>
       <c r="G38" t="s">
         <v>182</v>
@@ -3042,36 +3054,36 @@
         <v>188</v>
       </c>
       <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" t="s">
         <v>189</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
         <v>190</v>
       </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="F40" t="n">
+        <v>0.517761394595505</v>
+      </c>
+      <c r="G40" t="s">
         <v>191</v>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="H40" t="n">
+        <v>0.190473772503941</v>
+      </c>
+      <c r="I40" t="s">
         <v>192</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>193</v>
+      </c>
+      <c r="B41" t="s">
         <v>194</v>
-      </c>
-      <c r="B41" t="s">
-        <v>26</v>
       </c>
       <c r="C41" t="s">
         <v>195</v>
@@ -3086,39 +3098,39 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>22</v>
+        <v>197</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B42" t="s">
         <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>201</v>
+        <v>22</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="s">
         <v>202</v>
@@ -3132,33 +3144,33 @@
         <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>204</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F43" t="n">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>22</v>
+        <v>206</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="C44" t="s">
         <v>22</v>
@@ -3167,190 +3179,190 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="H44" t="n">
-        <v>0.554369703815855</v>
+        <v>0.455054233923411</v>
       </c>
       <c r="I44" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B45" t="s">
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>213</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0.461974753179879</v>
       </c>
       <c r="G45" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0.761667602094109</v>
       </c>
       <c r="I45" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="C46" t="s">
-        <v>215</v>
+        <v>22</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F46" t="n">
-        <v>0.761667602094109</v>
+        <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H46" t="n">
-        <v>0.169951014035129</v>
+        <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C47" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>22</v>
+        <v>224</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.761667602094109</v>
       </c>
       <c r="G47" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0.169951014035129</v>
       </c>
       <c r="I47" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s">
-        <v>224</v>
+        <v>26</v>
       </c>
       <c r="C48" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>226</v>
+        <v>22</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B49" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C49" t="s">
-        <v>230</v>
+        <v>22</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F49" t="n">
-        <v>0.280201851816773</v>
+        <v>1</v>
       </c>
       <c r="G49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H49" t="n">
-        <v>0.761667602094109</v>
+        <v>0.931618616129238</v>
       </c>
       <c r="I49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>235</v>
+        <v>22</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" t="s">
         <v>236</v>
       </c>
       <c r="F50" t="n">
-        <v>0.537764103352331</v>
+        <v>0.914001122512931</v>
       </c>
       <c r="G50" t="s">
         <v>237</v>
       </c>
       <c r="H50" t="n">
-        <v>0.119991390503082</v>
+        <v>0.554369703815855</v>
       </c>
       <c r="I50" t="s">
         <v>238</v>
@@ -3361,94 +3373,94 @@
         <v>239</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>240</v>
       </c>
       <c r="C51" t="s">
-        <v>22</v>
+        <v>241</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F51" t="n">
-        <v>0.931618616129238</v>
+        <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H51" t="n">
-        <v>0.931618616129238</v>
+        <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B52" t="s">
         <v>146</v>
       </c>
       <c r="C52" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0924667556050435</v>
+        <v>0.152451906798665</v>
       </c>
       <c r="G52" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H52" t="n">
         <v>0.0924667556050435</v>
       </c>
       <c r="I52" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C53" t="s">
-        <v>22</v>
+        <v>251</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0.197832357823317</v>
       </c>
       <c r="G53" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0.119991390503082</v>
       </c>
       <c r="I53" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B54" t="s">
-        <v>210</v>
+        <v>74</v>
       </c>
       <c r="C54" t="s">
         <v>22</v>
@@ -3457,201 +3469,201 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0.931618616129238</v>
       </c>
       <c r="G54" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H54" t="n">
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="C55" t="s">
-        <v>22</v>
+        <v>260</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0.646764654451831</v>
       </c>
       <c r="G55" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0.233125285421556</v>
       </c>
       <c r="I55" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F56" t="n">
-        <v>0.461974753179879</v>
+        <v>0.88662311581597</v>
       </c>
       <c r="G56" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="H56" t="n">
-        <v>0.461974753179879</v>
+        <v>0.326170416376062</v>
       </c>
       <c r="I56" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B57" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F57" t="n">
-        <v>0.384358616812558</v>
+        <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="H57" t="n">
         <v>0.233125285421556</v>
       </c>
       <c r="I57" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>218</v>
       </c>
       <c r="C58" t="s">
-        <v>271</v>
+        <v>22</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F58" t="n">
-        <v>0.326170416376062</v>
+        <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H58" t="n">
-        <v>0.326170416376062</v>
+        <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C59" t="s">
-        <v>276</v>
+        <v>22</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F59" t="n">
-        <v>0.190473772503941</v>
+        <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H59" t="n">
-        <v>0.190473772503941</v>
+        <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B60" t="s">
         <v>36</v>
       </c>
       <c r="C60" t="s">
-        <v>22</v>
+        <v>283</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0.280201851816773</v>
       </c>
       <c r="G60" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0.461974753179879</v>
       </c>
       <c r="I60" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B61" t="s">
-        <v>146</v>
+        <v>36</v>
       </c>
       <c r="C61" t="s">
         <v>22</v>
@@ -3660,169 +3672,169 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F61" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="H61" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B62" t="s">
-        <v>36</v>
+        <v>146</v>
       </c>
       <c r="C62" t="s">
-        <v>289</v>
+        <v>22</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F62" t="n">
-        <v>0.169951014035129</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G62" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H62" t="n">
-        <v>0.280201851816773</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I62" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C63" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>22</v>
+        <v>297</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="I63" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C64" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D64" t="n">
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0.169951014035129</v>
       </c>
       <c r="G64" t="s">
-        <v>22</v>
+        <v>303</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.280201851816773</v>
       </c>
       <c r="I64" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B65" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>303</v>
+        <v>22</v>
       </c>
       <c r="F65" t="n">
-        <v>0.669620389113773</v>
+        <v>0</v>
       </c>
       <c r="G65" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H65" t="n">
-        <v>0.406145296366207</v>
+        <v>1</v>
       </c>
       <c r="I65" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B66" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F66" t="n">
-        <v>0.633700227115744</v>
+        <v>1</v>
       </c>
       <c r="G66" t="s">
-        <v>309</v>
+        <v>22</v>
       </c>
       <c r="H66" t="n">
-        <v>0.384358616812558</v>
+        <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B67" t="s">
         <v>26</v>
@@ -3834,233 +3846,233 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>22</v>
+        <v>315</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.276004344706594</v>
       </c>
       <c r="I67" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B68" t="s">
         <v>56</v>
       </c>
       <c r="C68" t="s">
-        <v>314</v>
+        <v>22</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="F68" t="n">
-        <v>0.384358616812558</v>
+        <v>0.554369703815855</v>
       </c>
       <c r="G68" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H68" t="n">
-        <v>0.233125285421556</v>
+        <v>0.914001122512931</v>
       </c>
       <c r="I68" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B69" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C69" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D69" t="n">
         <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0.314038160237745</v>
       </c>
       <c r="G69" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>0.115528182894769</v>
       </c>
       <c r="I69" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B70" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="C70" t="s">
-        <v>22</v>
+        <v>327</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F70" t="n">
-        <v>0.554369703815855</v>
+        <v>0.237931419649181</v>
       </c>
       <c r="G70" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H70" t="n">
-        <v>0.914001122512931</v>
+        <v>0.384358616812558</v>
       </c>
       <c r="I70" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B71" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D71" t="n">
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F71" t="n">
-        <v>0.197832357823317</v>
+        <v>0.119991390503082</v>
       </c>
       <c r="G71" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H71" t="n">
         <v>0.537764103352331</v>
       </c>
       <c r="I71" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C72" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F72" t="n">
-        <v>0.115528182894769</v>
+        <v>0.406145296366207</v>
       </c>
       <c r="G72" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="H72" t="n">
-        <v>0.115528182894769</v>
+        <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B73" t="s">
-        <v>338</v>
+        <v>74</v>
       </c>
       <c r="C73" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D73" t="n">
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>0.537764103352331</v>
       </c>
       <c r="G73" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H73" t="n">
-        <v>0.755081337596291</v>
+        <v>0.197832357823317</v>
       </c>
       <c r="I73" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B74" t="s">
-        <v>62</v>
+        <v>347</v>
       </c>
       <c r="C74" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D74" t="n">
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F74" t="n">
-        <v>0.119991390503082</v>
+        <v>1</v>
       </c>
       <c r="G74" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H74" t="n">
-        <v>0.197832357823317</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I74" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B75" t="s">
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -4072,224 +4084,224 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H75" t="n">
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B76" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C76" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>354</v>
+        <v>22</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B77" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C77" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
       </c>
       <c r="E77" t="s">
-        <v>359</v>
+        <v>22</v>
       </c>
       <c r="F77" t="n">
-        <v>0.141397633162432</v>
+        <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H77" t="n">
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B78" t="s">
-        <v>210</v>
+        <v>365</v>
       </c>
       <c r="C78" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F78" t="n">
-        <v>0.910108467846823</v>
+        <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="H78" t="n">
-        <v>0.203072648183104</v>
+        <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B79" t="s">
-        <v>368</v>
+        <v>218</v>
       </c>
       <c r="C79" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>0.372647446451695</v>
       </c>
       <c r="G79" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>0.203072648183104</v>
       </c>
       <c r="I79" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B80" t="s">
-        <v>26</v>
+        <v>218</v>
       </c>
       <c r="C80" t="s">
-        <v>22</v>
+        <v>376</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>22</v>
+        <v>378</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>0.552008689413187</v>
       </c>
       <c r="I80" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B81" t="s">
-        <v>368</v>
+        <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>376</v>
+        <v>22</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>0.101536324091552</v>
       </c>
       <c r="I81" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B82" t="s">
-        <v>26</v>
+        <v>365</v>
       </c>
       <c r="C82" t="s">
-        <v>22</v>
+        <v>385</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>22</v>
+        <v>386</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="H82" t="n">
         <v>1</v>
       </c>
       <c r="I82" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B83" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="C83" t="s">
         <v>22</v>
@@ -4298,169 +4310,169 @@
         <v>0</v>
       </c>
       <c r="E83" t="s">
-        <v>383</v>
+        <v>22</v>
       </c>
       <c r="F83" t="n">
-        <v>0.336242222180128</v>
+        <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="H83" t="n">
-        <v>0.336242222180128</v>
+        <v>1</v>
       </c>
       <c r="I83" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B84" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C84" t="s">
-        <v>387</v>
+        <v>22</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="F84" t="n">
-        <v>0.141397633162432</v>
+        <v>0.336242222180128</v>
       </c>
       <c r="G84" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H84" t="n">
-        <v>0.141397633162432</v>
+        <v>0.336242222180128</v>
       </c>
       <c r="I84" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B85" t="s">
         <v>50</v>
       </c>
       <c r="C85" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F85" t="n">
-        <v>0.406145296366207</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="G85" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="H85" t="n">
         <v>0.669620389113773</v>
       </c>
       <c r="I85" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B86" t="s">
-        <v>210</v>
+        <v>85</v>
       </c>
       <c r="C86" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="D86" t="n">
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>397</v>
+        <v>22</v>
       </c>
       <c r="F86" t="n">
-        <v>0.552008689413187</v>
+        <v>0</v>
       </c>
       <c r="G86" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="H86" t="n">
-        <v>0.910108467846823</v>
+        <v>0.141397633162432</v>
       </c>
       <c r="I86" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B87" t="s">
-        <v>90</v>
+        <v>218</v>
       </c>
       <c r="C87" t="s">
-        <v>22</v>
+        <v>405</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="F87" t="n">
-        <v>0.203941216842155</v>
+        <v>0.614391771436997</v>
       </c>
       <c r="G87" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="H87" t="n">
-        <v>0.203941216842155</v>
+        <v>0.910108467846823</v>
       </c>
       <c r="I87" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B88" t="s">
-        <v>210</v>
+        <v>56</v>
       </c>
       <c r="C88" t="s">
-        <v>405</v>
+        <v>22</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F88" t="n">
-        <v>0.334810194556887</v>
+        <v>0.203941216842155</v>
       </c>
       <c r="G88" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="H88" t="n">
-        <v>0.552008689413187</v>
+        <v>0.203941216842155</v>
       </c>
       <c r="I88" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="B89" t="s">
         <v>26</v>
@@ -4472,30 +4484,30 @@
         <v>0</v>
       </c>
       <c r="E89" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="s">
-        <v>22</v>
+        <v>415</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>0.167405097278443</v>
       </c>
       <c r="I89" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B90" t="s">
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
@@ -4513,41 +4525,41 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B91" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C91" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="F91" t="n">
-        <v>0.233125285421556</v>
+        <v>0.392282592543483</v>
       </c>
       <c r="G91" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="H91" t="n">
         <v>0.141397633162432</v>
       </c>
       <c r="I91" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B92" t="s">
         <v>26</v>
@@ -4565,18 +4577,18 @@
         <v>0</v>
       </c>
       <c r="G92" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="H92" t="n">
         <v>1</v>
       </c>
       <c r="I92" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B93" t="s">
         <v>10</v>
@@ -4588,39 +4600,37 @@
         <v>0</v>
       </c>
       <c r="E93" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="F93" t="n">
         <v>0.377540668798145</v>
       </c>
       <c r="G93" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="H93" t="n">
         <v>1</v>
       </c>
       <c r="I93" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>423</v>
-      </c>
-      <c r="B94" t="s">
-        <v>424</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="B94"/>
       <c r="C94" t="s">
-        <v>425</v>
+        <v>310</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>354</v>
+        <v>22</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="s">
         <v>22</v>
@@ -4629,16 +4639,18 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>426</v>
+        <v>310</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>427</v>
-      </c>
-      <c r="B95"/>
+        <v>430</v>
+      </c>
+      <c r="B95" t="s">
+        <v>56</v>
+      </c>
       <c r="C95" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
@@ -4656,18 +4668,18 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B96" t="s">
-        <v>368</v>
+        <v>26</v>
       </c>
       <c r="C96" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
@@ -4685,18 +4697,18 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B97" t="s">
-        <v>90</v>
+        <v>365</v>
       </c>
       <c r="C97" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
@@ -4714,16 +4726,18 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>430</v>
-      </c>
-      <c r="B98"/>
+        <v>433</v>
+      </c>
+      <c r="B98" t="s">
+        <v>434</v>
+      </c>
       <c r="C98" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="D98" t="n">
         <v>1</v>
@@ -4741,16 +4755,18 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>431</v>
-      </c>
-      <c r="B99"/>
+        <v>435</v>
+      </c>
+      <c r="B99" t="s">
+        <v>436</v>
+      </c>
       <c r="C99" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="D99" t="n">
         <v>1</v>
@@ -4768,19 +4784,21 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>432</v>
-      </c>
-      <c r="B100"/>
+        <v>437</v>
+      </c>
+      <c r="B100" t="s">
+        <v>26</v>
+      </c>
       <c r="C100" t="s">
-        <v>298</v>
+        <v>22</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="s">
         <v>22</v>
@@ -4789,535 +4807,535 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>22</v>
+        <v>220</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" t="s">
-        <v>298</v>
+        <v>220</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B101" t="s">
-        <v>26</v>
+        <v>347</v>
       </c>
       <c r="C101" t="s">
-        <v>22</v>
+        <v>439</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="s">
-        <v>22</v>
+        <v>440</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G101" t="s">
-        <v>212</v>
+        <v>441</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
       </c>
       <c r="I101" t="s">
-        <v>212</v>
+        <v>442</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="B102" t="s">
-        <v>338</v>
+        <v>444</v>
       </c>
       <c r="C102" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
       </c>
       <c r="E102" t="s">
-        <v>436</v>
+        <v>22</v>
       </c>
       <c r="F102" t="n">
-        <v>0.755081337596291</v>
+        <v>0</v>
       </c>
       <c r="G102" t="s">
-        <v>437</v>
+        <v>22</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B103" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="C103" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
       </c>
       <c r="E103" t="s">
-        <v>441</v>
+        <v>22</v>
       </c>
       <c r="F103" t="n">
-        <v>0.203072648183104</v>
+        <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="H103" t="n">
         <v>0.334810194556887</v>
       </c>
       <c r="I103" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="B104" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="C104" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
       </c>
       <c r="E104" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F104" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="G104" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="H104" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="I104" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B105" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C105" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
       </c>
       <c r="E105" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F105" t="n">
         <v>0.755081337596291</v>
       </c>
       <c r="G105" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="H105" t="n">
         <v>0.755081337596291</v>
       </c>
       <c r="I105" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B106" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C106" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F106" t="n">
         <v>0.74529489290339</v>
       </c>
       <c r="G106" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="H106" t="n">
         <v>0.74529489290339</v>
       </c>
       <c r="I106" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B107" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="C107" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="D107" t="n">
         <v>1</v>
       </c>
       <c r="E107" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F107" t="n">
         <v>1</v>
       </c>
       <c r="G107" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="H107" t="n">
         <v>1</v>
       </c>
       <c r="I107" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B108" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C108" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="s">
-        <v>354</v>
+        <v>22</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G108" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
       </c>
       <c r="I108" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="B109" t="s">
-        <v>471</v>
+        <v>434</v>
       </c>
       <c r="C109" t="s">
-        <v>298</v>
+        <v>476</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>22</v>
+        <v>477</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="H109" t="n">
         <v>1</v>
       </c>
       <c r="I109" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="B110" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C110" t="s">
-        <v>476</v>
+        <v>310</v>
       </c>
       <c r="D110" t="n">
         <v>1</v>
       </c>
       <c r="E110" t="s">
-        <v>477</v>
+        <v>22</v>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="H110" t="n">
-        <v>0.921587657155495</v>
+        <v>1</v>
       </c>
       <c r="I110" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B111" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C111" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
       </c>
       <c r="E111" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
       </c>
       <c r="G111" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H111" t="n">
         <v>1</v>
       </c>
       <c r="I111" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B112" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C112" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
       </c>
       <c r="E112" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
       </c>
       <c r="I112" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B113" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C113" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D113" t="n">
         <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
       </c>
       <c r="G113" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="H113" t="n">
         <v>1</v>
       </c>
       <c r="I113" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B114" t="s">
-        <v>424</v>
+        <v>444</v>
       </c>
       <c r="C114" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F114" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="G114" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
       </c>
       <c r="I114" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B115" t="s">
-        <v>475</v>
+        <v>434</v>
       </c>
       <c r="C115" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
       </c>
       <c r="E115" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F115" t="n">
-        <v>0.921587657155495</v>
+        <v>1</v>
       </c>
       <c r="G115" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="H115" t="n">
         <v>1</v>
       </c>
       <c r="I115" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="B116" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C116" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D116" t="n">
         <v>1</v>
       </c>
       <c r="E116" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="F116" t="n">
-        <v>0.558971169677543</v>
+        <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="H116" t="n">
-        <v>0.558971169677543</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I116" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B117" t="s">
-        <v>467</v>
+        <v>434</v>
       </c>
       <c r="C117" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D117" t="n">
         <v>1</v>
       </c>
       <c r="E117" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F117" t="n">
-        <v>0.755081337596291</v>
+        <v>0.74529489290339</v>
       </c>
       <c r="G117" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="H117" t="n">
-        <v>0.755081337596291</v>
+        <v>0.74529489290339</v>
       </c>
       <c r="I117" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B118" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C118" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D118" t="n">
         <v>1</v>
       </c>
       <c r="E118" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
       </c>
       <c r="G118" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H118" t="n">
         <v>0.755081337596291</v>
       </c>
       <c r="I118" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>

--- a/content/post/drafts/weekly-picks/2025Ruka/men-points.xlsx
+++ b/content/post/drafts/weekly-picks/2025Ruka/men-points.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="439">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -509,6 +509,12 @@
     <t xml:space="preserve">44.7069829266329</t>
   </si>
   <si>
+    <t xml:space="preserve">Marcus Grate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.42514969696</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ville Ahonen</t>
   </si>
   <si>
@@ -521,18 +527,6 @@
     <t xml:space="preserve">43.9219175109499</t>
   </si>
   <si>
-    <t xml:space="preserve">Marcus Grate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.42514969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.85101791438463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5741317825753</t>
-  </si>
-  <si>
     <t xml:space="preserve">Beda Klee</t>
   </si>
   <si>
@@ -674,12 +668,6 @@
     <t xml:space="preserve">31.0234744538969</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.27131161382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7521628400737</t>
-  </si>
-  <si>
     <t xml:space="preserve">Elia Barp</t>
   </si>
   <si>
@@ -707,6 +695,12 @@
     <t xml:space="preserve">29.9948087372297</t>
   </si>
   <si>
+    <t xml:space="preserve">Oskar Svensson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6349484799327</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jan Stoelben</t>
   </si>
   <si>
@@ -719,18 +713,6 @@
     <t xml:space="preserve">29.4295446150294</t>
   </si>
   <si>
-    <t xml:space="preserve">Oskar Svensson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6349484799327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.796277264146794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8386712157859</t>
-  </si>
-  <si>
     <t xml:space="preserve">Irineu Esteve Altimiras</t>
   </si>
   <si>
@@ -914,6 +896,12 @@
     <t xml:space="preserve">19.9859032856022</t>
   </si>
   <si>
+    <t xml:space="preserve">Emil Danielsson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.842309343126</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paolo Ventura</t>
   </si>
   <si>
@@ -965,18 +953,6 @@
     <t xml:space="preserve">15.1277476797882</t>
   </si>
   <si>
-    <t xml:space="preserve">Emil Danielsson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.842309343126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.42609894337061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4162103997554</t>
-  </si>
-  <si>
     <t xml:space="preserve">Truls Gisselman</t>
   </si>
   <si>
@@ -1037,6 +1013,21 @@
     <t xml:space="preserve">12.964590197634</t>
   </si>
   <si>
+    <t xml:space="preserve">Miha Simenc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06462391322654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02590833096302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0905322441896</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jan-Friedrich Doerks</t>
   </si>
   <si>
@@ -1052,60 +1043,27 @@
     <t xml:space="preserve">10.9778334500089</t>
   </si>
   <si>
-    <t xml:space="preserve">Miha Simenc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06462391322654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02590833096302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.412736533098074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6777957110915</t>
-  </si>
-  <si>
     <t xml:space="preserve">Andreas Fjorden Ree</t>
   </si>
   <si>
     <t xml:space="preserve">10.1979073840123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92659577018902</t>
-  </si>
-  <si>
     <t xml:space="preserve">Joe Davies</t>
   </si>
   <si>
     <t xml:space="preserve">Great Britain</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.734936766045822</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.12614022329822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3912034572524</t>
-  </si>
-  <si>
     <t xml:space="preserve">Johnny Hagenbuch</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.326951575906619</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.69645538965557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36950381374895</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alvar Johannes Alev</t>
   </si>
   <si>
@@ -1115,13 +1073,22 @@
     <t xml:space="preserve">1.132098055202</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.836845989550548</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.20198326607999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49723533173144</t>
+    <t xml:space="preserve">7.33408132128199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jiri Tuz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10820362507409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99861335614241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1068169812165</t>
   </si>
   <si>
     <t xml:space="preserve">Adam Fellner</t>
@@ -1139,19 +1106,10 @@
     <t xml:space="preserve">6.45114868067011</t>
   </si>
   <si>
-    <t xml:space="preserve">Jiri Tuz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10820362507409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99861335614241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.680864362015024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42595261920148</t>
+    <t xml:space="preserve">Martin Himma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2950994223858</t>
   </si>
   <si>
     <t xml:space="preserve">Eero Rantala</t>
@@ -1160,27 +1118,6 @@
     <t xml:space="preserve">6.11588473260095</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.0275479839509585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08833674865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin Himma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.497537686362957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2950994223858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.447298978510162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35026275751268</t>
-  </si>
-  <si>
     <t xml:space="preserve">Miro Karppanen</t>
   </si>
   <si>
@@ -1193,10 +1130,13 @@
     <t xml:space="preserve">5.19804006775015</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.091226419935203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10681364781495</t>
+    <t xml:space="preserve">Raimo Vigants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37743149888155</t>
   </si>
   <si>
     <t xml:space="preserve">Max Hollmann</t>
@@ -1235,10 +1175,19 @@
     <t xml:space="preserve">0.703789850501424</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.10970797378858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86032143704402</t>
+    <t xml:space="preserve">2.9700294108326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miha Licef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.324478275824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauris Kaparkalejs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87523067218972</t>
   </si>
   <si>
     <t xml:space="preserve">Johan Ekberg</t>
@@ -1247,22 +1196,22 @@
     <t xml:space="preserve">1.87110517119952</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.0553316206665204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.815773550533</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ike Melnits</t>
   </si>
   <si>
     <t xml:space="preserve">1.71464530281497</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.045418947104851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66922635571012</t>
+    <t xml:space="preserve">Michael Earnhart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47455804041903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12235255059994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59691059101897</t>
   </si>
   <si>
     <t xml:space="preserve">Alexander Ståhlberg</t>
@@ -1271,19 +1220,28 @@
     <t xml:space="preserve">1.49299280422385</t>
   </si>
   <si>
-    <t xml:space="preserve">Michael Earnhart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47455804041903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12235255059994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.163921567771262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43298902324771</t>
+    <t xml:space="preserve">Andrej Renda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slovakia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38494595295992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mikayel Mikayelyan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armenia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.16867103410246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spartak Voskanyan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.08471183889821</t>
   </si>
   <si>
     <t xml:space="preserve">Veeti Pyykko</t>
@@ -1298,9 +1256,6 @@
     <t xml:space="preserve">0.432475340986727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161163727163487</t>
-  </si>
-  <si>
     <t xml:space="preserve">Imanol ROJO GARCIA</t>
   </si>
   <si>
@@ -1322,274 +1277,58 @@
     <t xml:space="preserve">Sandijs Suhanovs</t>
   </si>
   <si>
-    <t xml:space="preserve">Latvia</t>
+    <t xml:space="preserve">Bentley Walker-Broose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Australia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Büki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henri Roos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00522962162342083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seve De Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomas Dufek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nail Bashmakov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simeon Deyanov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgaria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dmytro Romanchenko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ukraine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dmytro Drahun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vladislav Kovalyov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Konya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olzhas Klimin</t>
   </si>
   <si>
     <t xml:space="preserve">Aleksi Parttimaa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miha Licef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.8687125507133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.30216099962986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.324478275824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.846395274519158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dmytro Romanchenko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ukraine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.997935759203038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomas Dufek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.03501808319774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.766650795579067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.8016688787768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raimo Vigants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.5817756409166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37743149888155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.53917743922851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.74352158126356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mikayel Mikayelyan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armenia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.53902447345779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.16867103410246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.138817513850874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.5091709532062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henri Roos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.02742815227766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00522962162342083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.840472378028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.86267090868268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauris Kaparkalejs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.72240141574297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87523067218972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.14241923595094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.98958997950419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bentley Walker-Broose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Australia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.48324695028333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.44152048384567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nail Bashmakov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.38594518278411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.61647708402643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.1621455554665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9.16456782227705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Büki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9.24501991240203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9.20329344596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spartak Voskanyan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.81530974350897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.08471183889821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.57501326217608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.3056111667868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrej Renda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slovakia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.62485695958292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38494595295992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9.23871920525471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-12.4786302118777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simeon Deyanov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulgaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.86857588517158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.381488428287874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.57335390615778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-12.8234182196172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dmytro Drahun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.26550169517895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.27010726545637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.34392586290516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-13.8795348235405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olzhas Klimin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.07577340280702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.61894810927428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.41955615606089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-14.1142776681422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Konya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.04266007237829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.91043195560366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.68287056104776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-15.6359625890297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vladislav Kovalyov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.12101413549816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.91278444474804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.29801146679828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.3318100470445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seve De Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.15195611409926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.62770263223595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.69490145587212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.4745602022073</t>
   </si>
 </sst>
 </file>
@@ -2880,17 +2619,17 @@
         <v>165</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
         <v>166</v>
       </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="s">
-        <v>167</v>
-      </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
@@ -2898,73 +2637,73 @@
         <v>22</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>167</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>168</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="s">
         <v>169</v>
       </c>
-      <c r="B35" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="s">
         <v>170</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="s">
-        <v>171</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B36" t="s">
         <v>146</v>
       </c>
       <c r="C36" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D36" t="n">
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F36" t="n">
         <v>0.0924667556050435</v>
       </c>
       <c r="G36" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H36" t="n">
         <v>0.152451906798665</v>
       </c>
       <c r="I36" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
@@ -2976,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -2988,186 +2727,186 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B38" t="s">
         <v>26</v>
       </c>
       <c r="C38" t="s">
+        <v>179</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="s">
+        <v>180</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
         <v>181</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="s">
-        <v>182</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B39" t="s">
         <v>26</v>
       </c>
       <c r="C39" t="s">
+        <v>183</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="s">
+        <v>184</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
         <v>185</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="s">
-        <v>186</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B40" t="s">
         <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D40" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F40" t="n">
         <v>0.517761394595505</v>
       </c>
       <c r="G40" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H40" t="n">
         <v>0.190473772503941</v>
       </c>
       <c r="I40" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>191</v>
+      </c>
+      <c r="B41" t="s">
+        <v>192</v>
+      </c>
+      <c r="C41" t="s">
         <v>193</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
         <v>194</v>
       </c>
-      <c r="C41" t="s">
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
         <v>195</v>
       </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
         <v>196</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
-        <v>197</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B42" t="s">
         <v>26</v>
       </c>
       <c r="C42" t="s">
+        <v>198</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
+        <v>199</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="s">
         <v>200</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="s">
-        <v>201</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>22</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B43" t="s">
         <v>26</v>
       </c>
       <c r="C43" t="s">
+        <v>202</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>203</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
         <v>204</v>
       </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
         <v>205</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>206</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B44" t="s">
         <v>26</v>
@@ -3179,117 +2918,117 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H44" t="n">
         <v>0.455054233923411</v>
       </c>
       <c r="I44" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B45" t="s">
         <v>36</v>
       </c>
       <c r="C45" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D45" t="n">
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F45" t="n">
         <v>0.461974753179879</v>
       </c>
       <c r="G45" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H45" t="n">
         <v>0.761667602094109</v>
       </c>
       <c r="I45" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>215</v>
+      </c>
+      <c r="B46" t="s">
+        <v>216</v>
+      </c>
+      <c r="C46" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="s">
         <v>217</v>
       </c>
-      <c r="B46" t="s">
-        <v>218</v>
-      </c>
-      <c r="C46" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="s">
-        <v>219</v>
-      </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="s">
-        <v>220</v>
+        <v>22</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B47" t="s">
         <v>36</v>
       </c>
       <c r="C47" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F47" t="n">
         <v>0.761667602094109</v>
       </c>
       <c r="G47" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H47" t="n">
         <v>0.169951014035129</v>
       </c>
       <c r="I47" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s">
         <v>26</v>
       </c>
       <c r="C48" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D48" t="n">
         <v>1</v>
@@ -3301,21 +3040,21 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="C49" t="s">
         <v>22</v>
@@ -3324,27 +3063,27 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0.914001122512931</v>
       </c>
       <c r="G49" t="s">
-        <v>233</v>
+        <v>22</v>
       </c>
       <c r="H49" t="n">
-        <v>0.931618616129238</v>
+        <v>0.554369703815855</v>
       </c>
       <c r="I49" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C50" t="s">
         <v>22</v>
@@ -3353,111 +3092,111 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="F50" t="n">
-        <v>0.914001122512931</v>
+        <v>1</v>
       </c>
       <c r="G50" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="H50" t="n">
-        <v>0.554369703815855</v>
+        <v>0.931618616129238</v>
       </c>
       <c r="I50" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B51" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C51" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D51" t="n">
         <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="H51" t="n">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B52" t="s">
         <v>146</v>
       </c>
       <c r="C52" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D52" t="n">
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="F52" t="n">
         <v>0.152451906798665</v>
       </c>
       <c r="G52" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="H52" t="n">
         <v>0.0924667556050435</v>
       </c>
       <c r="I52" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B53" t="s">
         <v>74</v>
       </c>
       <c r="C53" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D53" t="n">
         <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="F53" t="n">
         <v>0.197832357823317</v>
       </c>
       <c r="G53" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="H53" t="n">
         <v>0.119991390503082</v>
       </c>
       <c r="I53" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B54" t="s">
         <v>74</v>
@@ -3469,114 +3208,114 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="F54" t="n">
         <v>0.931618616129238</v>
       </c>
       <c r="G54" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="H54" t="n">
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B55" t="s">
         <v>85</v>
       </c>
       <c r="C55" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F55" t="n">
         <v>0.646764654451831</v>
       </c>
       <c r="G55" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="H55" t="n">
         <v>0.233125285421556</v>
       </c>
       <c r="I55" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B56" t="s">
         <v>74</v>
       </c>
       <c r="C56" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="F56" t="n">
         <v>0.88662311581597</v>
       </c>
       <c r="G56" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="H56" t="n">
         <v>0.326170416376062</v>
       </c>
       <c r="I56" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B57" t="s">
         <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D57" t="n">
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="H57" t="n">
         <v>0.233125285421556</v>
       </c>
       <c r="I57" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B58" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C58" t="s">
         <v>22</v>
@@ -3585,24 +3324,24 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="H58" t="n">
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B59" t="s">
         <v>74</v>
@@ -3614,53 +3353,53 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="H59" t="n">
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B60" t="s">
         <v>36</v>
       </c>
       <c r="C60" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D60" t="n">
         <v>1</v>
       </c>
       <c r="E60" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="F60" t="n">
         <v>0.280201851816773</v>
       </c>
       <c r="G60" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="H60" t="n">
         <v>0.461974753179879</v>
       </c>
       <c r="I60" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B61" t="s">
         <v>36</v>
@@ -3672,24 +3411,24 @@
         <v>0</v>
       </c>
       <c r="E61" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B62" t="s">
         <v>146</v>
@@ -3701,172 +3440,172 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F62" t="n">
         <v>0.755081337596291</v>
       </c>
       <c r="G62" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="H62" t="n">
         <v>0.755081337596291</v>
       </c>
       <c r="I62" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B63" t="s">
         <v>50</v>
       </c>
       <c r="C63" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="H63" t="n">
         <v>0.406145296366207</v>
       </c>
       <c r="I63" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B64" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C64" t="s">
-        <v>301</v>
+        <v>22</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="F64" t="n">
-        <v>0.169951014035129</v>
+        <v>0.554369703815855</v>
       </c>
       <c r="G64" t="s">
-        <v>303</v>
+        <v>22</v>
       </c>
       <c r="H64" t="n">
-        <v>0.280201851816773</v>
+        <v>0.914001122512931</v>
       </c>
       <c r="I64" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B65" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C65" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>22</v>
+        <v>298</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>0.169951014035129</v>
       </c>
       <c r="G65" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>0.280201851816773</v>
       </c>
       <c r="I65" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B66" t="s">
         <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>311</v>
+        <v>22</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="s">
-        <v>22</v>
+        <v>303</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="B67" t="s">
         <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>22</v>
+        <v>306</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="s">
-        <v>315</v>
+        <v>22</v>
       </c>
       <c r="H67" t="n">
-        <v>0.276004344706594</v>
+        <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B68" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
         <v>22</v>
@@ -3875,204 +3614,204 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="F68" t="n">
-        <v>0.554369703815855</v>
+        <v>1</v>
       </c>
       <c r="G68" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="H68" t="n">
-        <v>0.914001122512931</v>
+        <v>0.276004344706594</v>
       </c>
       <c r="I68" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="B69" t="s">
         <v>56</v>
       </c>
       <c r="C69" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D69" t="n">
         <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="F69" t="n">
         <v>0.314038160237745</v>
       </c>
       <c r="G69" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="H69" t="n">
         <v>0.115528182894769</v>
       </c>
       <c r="I69" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B70" t="s">
         <v>62</v>
       </c>
       <c r="C70" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="F70" t="n">
         <v>0.237931419649181</v>
       </c>
       <c r="G70" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="H70" t="n">
         <v>0.384358616812558</v>
       </c>
       <c r="I70" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B71" t="s">
         <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="D71" t="n">
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F71" t="n">
         <v>0.119991390503082</v>
       </c>
       <c r="G71" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="H71" t="n">
         <v>0.537764103352331</v>
       </c>
       <c r="I71" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B72" t="s">
         <v>50</v>
       </c>
       <c r="C72" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="D72" t="n">
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="F72" t="n">
         <v>0.406145296366207</v>
       </c>
       <c r="G72" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="H72" t="n">
         <v>1</v>
       </c>
       <c r="I72" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
+        <v>334</v>
       </c>
       <c r="C73" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D73" t="n">
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="F73" t="n">
-        <v>0.537764103352331</v>
+        <v>1</v>
       </c>
       <c r="G73" t="s">
-        <v>344</v>
+        <v>22</v>
       </c>
       <c r="H73" t="n">
-        <v>0.197832357823317</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I73" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="B74" t="s">
-        <v>347</v>
+        <v>74</v>
       </c>
       <c r="C74" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="D74" t="n">
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0.537764103352331</v>
       </c>
       <c r="G74" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="H74" t="n">
-        <v>0.755081337596291</v>
+        <v>0.197832357823317</v>
       </c>
       <c r="I74" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B75" t="s">
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
@@ -4084,24 +3823,24 @@
         <v>0</v>
       </c>
       <c r="G75" t="s">
-        <v>220</v>
+        <v>22</v>
       </c>
       <c r="H75" t="n">
         <v>1</v>
       </c>
       <c r="I75" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="B76" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C76" t="s">
-        <v>357</v>
+        <v>22</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
@@ -4113,24 +3852,24 @@
         <v>0</v>
       </c>
       <c r="G76" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
       </c>
       <c r="I76" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="B77" t="s">
         <v>62</v>
       </c>
       <c r="C77" t="s">
-        <v>361</v>
+        <v>22</v>
       </c>
       <c r="D77" t="n">
         <v>1</v>
@@ -4142,163 +3881,163 @@
         <v>0</v>
       </c>
       <c r="G77" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="H77" t="n">
         <v>1</v>
       </c>
       <c r="I77" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B78" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="C78" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>367</v>
+        <v>22</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
       </c>
       <c r="I78" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="B79" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C79" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="F79" t="n">
-        <v>0.372647446451695</v>
+        <v>1</v>
       </c>
       <c r="G79" t="s">
-        <v>373</v>
+        <v>22</v>
       </c>
       <c r="H79" t="n">
-        <v>0.203072648183104</v>
+        <v>0.552008689413187</v>
       </c>
       <c r="I79" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="B80" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C80" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D80" t="n">
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0.372647446451695</v>
       </c>
       <c r="G80" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="H80" t="n">
-        <v>0.552008689413187</v>
+        <v>0.203072648183104</v>
       </c>
       <c r="I80" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="B81" t="s">
-        <v>26</v>
+        <v>351</v>
       </c>
       <c r="C81" t="s">
         <v>22</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="s">
-        <v>382</v>
+        <v>22</v>
       </c>
       <c r="H81" t="n">
-        <v>0.101536324091552</v>
+        <v>1</v>
       </c>
       <c r="I81" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="B82" t="s">
-        <v>365</v>
+        <v>26</v>
       </c>
       <c r="C82" t="s">
-        <v>385</v>
+        <v>22</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" t="s">
-        <v>387</v>
+        <v>22</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0.101536324091552</v>
       </c>
       <c r="I82" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="B83" t="s">
         <v>26</v>
@@ -4316,18 +4055,18 @@
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="H83" t="n">
         <v>1</v>
       </c>
       <c r="I83" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="B84" t="s">
         <v>56</v>
@@ -4339,227 +4078,227 @@
         <v>0</v>
       </c>
       <c r="E84" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="F84" t="n">
         <v>0.336242222180128</v>
       </c>
       <c r="G84" t="s">
-        <v>393</v>
+        <v>22</v>
       </c>
       <c r="H84" t="n">
         <v>0.336242222180128</v>
       </c>
       <c r="I84" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="B85" t="s">
-        <v>50</v>
+        <v>373</v>
       </c>
       <c r="C85" t="s">
-        <v>396</v>
+        <v>22</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
       <c r="F85" t="n">
-        <v>0.669620389113773</v>
+        <v>1</v>
       </c>
       <c r="G85" t="s">
-        <v>398</v>
+        <v>22</v>
       </c>
       <c r="H85" t="n">
-        <v>0.669620389113773</v>
+        <v>1</v>
       </c>
       <c r="I85" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="C86" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="D86" t="n">
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>22</v>
+        <v>377</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="G86" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="H86" t="n">
-        <v>0.141397633162432</v>
+        <v>0.669620389113773</v>
       </c>
       <c r="I86" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="B87" t="s">
-        <v>218</v>
+        <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="D87" t="n">
         <v>1</v>
       </c>
       <c r="E87" t="s">
-        <v>406</v>
+        <v>22</v>
       </c>
       <c r="F87" t="n">
-        <v>0.614391771436997</v>
+        <v>0</v>
       </c>
       <c r="G87" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="H87" t="n">
-        <v>0.910108467846823</v>
+        <v>0.141397633162432</v>
       </c>
       <c r="I87" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
       <c r="B88" t="s">
-        <v>56</v>
+        <v>216</v>
       </c>
       <c r="C88" t="s">
-        <v>22</v>
+        <v>385</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="F88" t="n">
-        <v>0.203941216842155</v>
+        <v>0.614391771436997</v>
       </c>
       <c r="G88" t="s">
-        <v>411</v>
+        <v>22</v>
       </c>
       <c r="H88" t="n">
-        <v>0.203941216842155</v>
+        <v>0.910108467846823</v>
       </c>
       <c r="I88" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>334</v>
       </c>
       <c r="C89" t="s">
         <v>22</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>414</v>
+        <v>22</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G89" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="H89" t="n">
-        <v>0.167405097278443</v>
+        <v>1</v>
       </c>
       <c r="I89" t="s">
-        <v>416</v>
+        <v>389</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>417</v>
+        <v>390</v>
       </c>
       <c r="B90" t="s">
-        <v>26</v>
+        <v>373</v>
       </c>
       <c r="C90" t="s">
-        <v>418</v>
+        <v>22</v>
       </c>
       <c r="D90" t="n">
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>22</v>
+        <v>391</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="s">
         <v>22</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="B91" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C91" t="s">
-        <v>420</v>
+        <v>22</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>421</v>
+        <v>393</v>
       </c>
       <c r="F91" t="n">
-        <v>0.392282592543483</v>
+        <v>0.203941216842155</v>
       </c>
       <c r="G91" t="s">
-        <v>422</v>
+        <v>22</v>
       </c>
       <c r="H91" t="n">
-        <v>0.141397633162432</v>
+        <v>0.203941216842155</v>
       </c>
       <c r="I91" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
       <c r="B92" t="s">
         <v>26</v>
@@ -4571,57 +4310,59 @@
         <v>0</v>
       </c>
       <c r="E92" t="s">
-        <v>22</v>
+        <v>395</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="s">
-        <v>425</v>
+        <v>22</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0.167405097278443</v>
       </c>
       <c r="I92" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
       <c r="B93" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="C93" t="s">
-        <v>22</v>
+        <v>397</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>427</v>
+        <v>398</v>
       </c>
       <c r="F93" t="n">
-        <v>0.377540668798145</v>
+        <v>0.392282592543483</v>
       </c>
       <c r="G93" t="s">
-        <v>220</v>
+        <v>22</v>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>0.141397633162432</v>
       </c>
       <c r="I93" t="s">
-        <v>428</v>
+        <v>399</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>429</v>
-      </c>
-      <c r="B94"/>
+        <v>400</v>
+      </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
       <c r="C94" t="s">
-        <v>310</v>
+        <v>401</v>
       </c>
       <c r="D94" t="n">
         <v>1</v>
@@ -4639,108 +4380,108 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>310</v>
+        <v>401</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>430</v>
+        <v>402</v>
       </c>
       <c r="B95" t="s">
-        <v>56</v>
+        <v>403</v>
       </c>
       <c r="C95" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>22</v>
+        <v>404</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="s">
         <v>22</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="s">
-        <v>310</v>
+        <v>404</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="B96" t="s">
-        <v>26</v>
+        <v>406</v>
       </c>
       <c r="C96" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="D96" t="n">
         <v>1</v>
       </c>
       <c r="E96" t="s">
-        <v>22</v>
+        <v>407</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="G96" t="s">
         <v>22</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I96" t="s">
-        <v>310</v>
+        <v>407</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="B97" t="s">
-        <v>365</v>
+        <v>406</v>
       </c>
       <c r="C97" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="D97" t="n">
         <v>1</v>
       </c>
       <c r="E97" t="s">
-        <v>22</v>
+        <v>409</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="s">
         <v>22</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" t="s">
-        <v>310</v>
+        <v>409</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>433</v>
+        <v>410</v>
       </c>
       <c r="B98" t="s">
-        <v>434</v>
+        <v>26</v>
       </c>
       <c r="C98" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="s">
         <v>22</v>
@@ -4749,56 +4490,54 @@
         <v>0</v>
       </c>
       <c r="G98" t="s">
-        <v>22</v>
+        <v>411</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="s">
-        <v>310</v>
+        <v>411</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="B99" t="s">
-        <v>436</v>
+        <v>10</v>
       </c>
       <c r="C99" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>22</v>
+        <v>413</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>0.377540668798145</v>
       </c>
       <c r="G99" t="s">
         <v>22</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="s">
-        <v>310</v>
+        <v>413</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>437</v>
-      </c>
-      <c r="B100" t="s">
-        <v>26</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="B100"/>
       <c r="C100" t="s">
-        <v>22</v>
+        <v>306</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" t="s">
         <v>22</v>
@@ -4807,53 +4546,53 @@
         <v>0</v>
       </c>
       <c r="G100" t="s">
-        <v>220</v>
+        <v>22</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>220</v>
+        <v>306</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="B101" t="s">
-        <v>347</v>
+        <v>56</v>
       </c>
       <c r="C101" t="s">
-        <v>439</v>
+        <v>306</v>
       </c>
       <c r="D101" t="n">
         <v>1</v>
       </c>
       <c r="E101" t="s">
-        <v>440</v>
+        <v>22</v>
       </c>
       <c r="F101" t="n">
-        <v>0.755081337596291</v>
+        <v>0</v>
       </c>
       <c r="G101" t="s">
-        <v>441</v>
+        <v>22</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>442</v>
+        <v>306</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>443</v>
+        <v>416</v>
       </c>
       <c r="B102" t="s">
-        <v>444</v>
+        <v>26</v>
       </c>
       <c r="C102" t="s">
-        <v>445</v>
+        <v>306</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -4871,18 +4610,18 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>445</v>
+        <v>306</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>446</v>
+        <v>417</v>
       </c>
       <c r="B103" t="s">
-        <v>218</v>
+        <v>351</v>
       </c>
       <c r="C103" t="s">
-        <v>447</v>
+        <v>306</v>
       </c>
       <c r="D103" t="n">
         <v>1</v>
@@ -4894,198 +4633,198 @@
         <v>0</v>
       </c>
       <c r="G103" t="s">
-        <v>448</v>
+        <v>22</v>
       </c>
       <c r="H103" t="n">
-        <v>0.334810194556887</v>
+        <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>449</v>
+        <v>306</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>450</v>
+        <v>418</v>
       </c>
       <c r="B104" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="C104" t="s">
-        <v>451</v>
+        <v>306</v>
       </c>
       <c r="D104" t="n">
         <v>1</v>
       </c>
       <c r="E104" t="s">
-        <v>452</v>
+        <v>22</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="s">
-        <v>453</v>
+        <v>22</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>454</v>
+        <v>306</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>455</v>
+        <v>420</v>
       </c>
       <c r="B105" t="s">
-        <v>456</v>
+        <v>373</v>
       </c>
       <c r="C105" t="s">
-        <v>457</v>
+        <v>306</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
       </c>
       <c r="E105" t="s">
-        <v>458</v>
+        <v>22</v>
       </c>
       <c r="F105" t="n">
-        <v>0.755081337596291</v>
+        <v>0</v>
       </c>
       <c r="G105" t="s">
-        <v>459</v>
+        <v>22</v>
       </c>
       <c r="H105" t="n">
-        <v>0.755081337596291</v>
+        <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>460</v>
+        <v>306</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>461</v>
+        <v>421</v>
       </c>
       <c r="B106" t="s">
-        <v>365</v>
+        <v>422</v>
       </c>
       <c r="C106" t="s">
-        <v>462</v>
+        <v>306</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>463</v>
+        <v>22</v>
       </c>
       <c r="F106" t="n">
-        <v>0.74529489290339</v>
+        <v>0</v>
       </c>
       <c r="G106" t="s">
-        <v>464</v>
+        <v>22</v>
       </c>
       <c r="H106" t="n">
-        <v>0.74529489290339</v>
+        <v>1</v>
       </c>
       <c r="I106" t="s">
-        <v>465</v>
+        <v>306</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>466</v>
+        <v>423</v>
       </c>
       <c r="B107" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="C107" t="s">
-        <v>467</v>
+        <v>306</v>
       </c>
       <c r="D107" t="n">
         <v>1</v>
       </c>
       <c r="E107" t="s">
-        <v>468</v>
+        <v>22</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G107" t="s">
-        <v>469</v>
+        <v>22</v>
       </c>
       <c r="H107" t="n">
         <v>1</v>
       </c>
       <c r="I107" t="s">
-        <v>470</v>
+        <v>306</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>471</v>
+        <v>425</v>
       </c>
       <c r="B108" t="s">
-        <v>472</v>
+        <v>351</v>
       </c>
       <c r="C108" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="s">
-        <v>22</v>
+        <v>426</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>0.74529489290339</v>
       </c>
       <c r="G108" t="s">
-        <v>473</v>
+        <v>22</v>
       </c>
       <c r="H108" t="n">
-        <v>1</v>
+        <v>0.74529489290339</v>
       </c>
       <c r="I108" t="s">
-        <v>474</v>
+        <v>426</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>475</v>
+        <v>427</v>
       </c>
       <c r="B109" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C109" t="s">
-        <v>476</v>
+        <v>22</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>477</v>
+        <v>22</v>
       </c>
       <c r="F109" t="n">
         <v>1</v>
       </c>
       <c r="G109" t="s">
-        <v>478</v>
+        <v>22</v>
       </c>
       <c r="H109" t="n">
-        <v>1</v>
+        <v>0.755081337596291</v>
       </c>
       <c r="I109" t="s">
-        <v>479</v>
+        <v>22</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>480</v>
+        <v>428</v>
       </c>
       <c r="B110" t="s">
-        <v>481</v>
+        <v>216</v>
       </c>
       <c r="C110" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="D110" t="n">
         <v>1</v>
@@ -5097,245 +4836,245 @@
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>482</v>
+        <v>22</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>0.334810194556887</v>
       </c>
       <c r="I110" t="s">
-        <v>483</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>484</v>
+        <v>429</v>
       </c>
       <c r="B111" t="s">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="C111" t="s">
-        <v>485</v>
+        <v>22</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
       </c>
       <c r="E111" t="s">
-        <v>486</v>
+        <v>22</v>
       </c>
       <c r="F111" t="n">
         <v>1</v>
       </c>
       <c r="G111" t="s">
-        <v>487</v>
+        <v>22</v>
       </c>
       <c r="H111" t="n">
         <v>1</v>
       </c>
       <c r="I111" t="s">
-        <v>488</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>489</v>
+        <v>430</v>
       </c>
       <c r="B112" t="s">
-        <v>490</v>
+        <v>431</v>
       </c>
       <c r="C112" t="s">
-        <v>491</v>
+        <v>22</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
       </c>
       <c r="E112" t="s">
-        <v>492</v>
+        <v>22</v>
       </c>
       <c r="F112" t="n">
         <v>1</v>
       </c>
       <c r="G112" t="s">
-        <v>493</v>
+        <v>22</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
       </c>
       <c r="I112" t="s">
-        <v>494</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>495</v>
+        <v>432</v>
       </c>
       <c r="B113" t="s">
-        <v>496</v>
+        <v>433</v>
       </c>
       <c r="C113" t="s">
-        <v>497</v>
+        <v>22</v>
       </c>
       <c r="D113" t="n">
         <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>498</v>
+        <v>22</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="s">
-        <v>499</v>
+        <v>22</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>500</v>
+        <v>22</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>501</v>
+        <v>434</v>
       </c>
       <c r="B114" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="C114" t="s">
-        <v>502</v>
+        <v>22</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>503</v>
+        <v>22</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
       </c>
       <c r="G114" t="s">
-        <v>504</v>
+        <v>22</v>
       </c>
       <c r="H114" t="n">
         <v>1</v>
       </c>
       <c r="I114" t="s">
-        <v>505</v>
+        <v>22</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>506</v>
+        <v>435</v>
       </c>
       <c r="B115" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="C115" t="s">
-        <v>507</v>
+        <v>22</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
       </c>
       <c r="E115" t="s">
-        <v>508</v>
+        <v>22</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>0.74529489290339</v>
       </c>
       <c r="G115" t="s">
-        <v>509</v>
+        <v>22</v>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>0.74529489290339</v>
       </c>
       <c r="I115" t="s">
-        <v>510</v>
+        <v>22</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>511</v>
+        <v>436</v>
       </c>
       <c r="B116" t="s">
-        <v>481</v>
+        <v>424</v>
       </c>
       <c r="C116" t="s">
-        <v>512</v>
+        <v>22</v>
       </c>
       <c r="D116" t="n">
         <v>1</v>
       </c>
       <c r="E116" t="s">
-        <v>513</v>
+        <v>22</v>
       </c>
       <c r="F116" t="n">
         <v>1</v>
       </c>
       <c r="G116" t="s">
-        <v>514</v>
+        <v>22</v>
       </c>
       <c r="H116" t="n">
         <v>0.755081337596291</v>
       </c>
       <c r="I116" t="s">
-        <v>515</v>
+        <v>22</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>516</v>
+        <v>437</v>
       </c>
       <c r="B117" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="C117" t="s">
-        <v>517</v>
+        <v>22</v>
       </c>
       <c r="D117" t="n">
         <v>1</v>
       </c>
       <c r="E117" t="s">
-        <v>518</v>
+        <v>22</v>
       </c>
       <c r="F117" t="n">
-        <v>0.74529489290339</v>
+        <v>1</v>
       </c>
       <c r="G117" t="s">
-        <v>519</v>
+        <v>22</v>
       </c>
       <c r="H117" t="n">
-        <v>0.74529489290339</v>
+        <v>1</v>
       </c>
       <c r="I117" t="s">
-        <v>520</v>
+        <v>22</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>521</v>
+        <v>438</v>
       </c>
       <c r="B118" t="s">
-        <v>472</v>
+        <v>26</v>
       </c>
       <c r="C118" t="s">
-        <v>522</v>
+        <v>22</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>523</v>
+        <v>22</v>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>524</v>
+        <v>22</v>
       </c>
       <c r="H118" t="n">
-        <v>0.755081337596291</v>
+        <v>1</v>
       </c>
       <c r="I118" t="s">
-        <v>525</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
